--- a/LME/parser/westmetall/data/LME_westmetall_db.xlsx
+++ b/LME/parser/westmetall/data/LME_westmetall_db.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1190"/>
+  <dimension ref="A1:H1191"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -31336,6 +31336,32 @@
         <v>53755</v>
       </c>
     </row>
+    <row r="1191" spans="1:8">
+      <c r="A1191" s="1">
+        <v>1189</v>
+      </c>
+      <c r="B1191" s="2">
+        <v>46279</v>
+      </c>
+      <c r="C1191">
+        <v>3311</v>
+      </c>
+      <c r="D1191">
+        <v>14044</v>
+      </c>
+      <c r="E1191">
+        <v>1834</v>
+      </c>
+      <c r="F1191">
+        <v>16205</v>
+      </c>
+      <c r="G1191">
+        <v>3951</v>
+      </c>
+      <c r="H1191">
+        <v>52200</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/westmetall/data/LME_westmetall_db.xlsx
+++ b/LME/parser/westmetall/data/LME_westmetall_db.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1191"/>
+  <dimension ref="A1:H1192"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -31362,6 +31362,32 @@
         <v>52200</v>
       </c>
     </row>
+    <row r="1192" spans="1:8">
+      <c r="A1192" s="1">
+        <v>1190</v>
+      </c>
+      <c r="B1192" s="2">
+        <v>46280</v>
+      </c>
+      <c r="C1192">
+        <v>3260</v>
+      </c>
+      <c r="D1192">
+        <v>14045</v>
+      </c>
+      <c r="E1192">
+        <v>1829</v>
+      </c>
+      <c r="F1192">
+        <v>16135</v>
+      </c>
+      <c r="G1192">
+        <v>3922</v>
+      </c>
+      <c r="H1192">
+        <v>51800</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/westmetall/data/LME_westmetall_db.xlsx
+++ b/LME/parser/westmetall/data/LME_westmetall_db.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1192"/>
+  <dimension ref="A1:H1193"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -31388,6 +31388,32 @@
         <v>51800</v>
       </c>
     </row>
+    <row r="1193" spans="1:8">
+      <c r="A1193" s="1">
+        <v>1191</v>
+      </c>
+      <c r="B1193" s="2">
+        <v>46281</v>
+      </c>
+      <c r="C1193">
+        <v>3310</v>
+      </c>
+      <c r="D1193">
+        <v>14227</v>
+      </c>
+      <c r="E1193">
+        <v>1848</v>
+      </c>
+      <c r="F1193">
+        <v>16090</v>
+      </c>
+      <c r="G1193">
+        <v>3937</v>
+      </c>
+      <c r="H1193">
+        <v>52310</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/westmetall/data/LME_westmetall_db.xlsx
+++ b/LME/parser/westmetall/data/LME_westmetall_db.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1193"/>
+  <dimension ref="A1:H1194"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -31414,6 +31414,32 @@
         <v>52310</v>
       </c>
     </row>
+    <row r="1194" spans="1:8">
+      <c r="A1194" s="1">
+        <v>1192</v>
+      </c>
+      <c r="B1194" s="2">
+        <v>46282</v>
+      </c>
+      <c r="C1194">
+        <v>3303.5</v>
+      </c>
+      <c r="D1194">
+        <v>14400.5</v>
+      </c>
+      <c r="E1194">
+        <v>1862</v>
+      </c>
+      <c r="F1194">
+        <v>16170</v>
+      </c>
+      <c r="G1194">
+        <v>3941</v>
+      </c>
+      <c r="H1194">
+        <v>53000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/westmetall/data/LME_westmetall_db.xlsx
+++ b/LME/parser/westmetall/data/LME_westmetall_db.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1194"/>
+  <dimension ref="A1:H1195"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -31440,6 +31440,32 @@
         <v>53000</v>
       </c>
     </row>
+    <row r="1195" spans="1:8">
+      <c r="A1195" s="1">
+        <v>1193</v>
+      </c>
+      <c r="B1195" s="2">
+        <v>46283</v>
+      </c>
+      <c r="C1195">
+        <v>3285</v>
+      </c>
+      <c r="D1195">
+        <v>14529</v>
+      </c>
+      <c r="E1195">
+        <v>1868</v>
+      </c>
+      <c r="F1195">
+        <v>16055</v>
+      </c>
+      <c r="G1195">
+        <v>4010</v>
+      </c>
+      <c r="H1195">
+        <v>53600</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/westmetall/data/LME_westmetall_db.xlsx
+++ b/LME/parser/westmetall/data/LME_westmetall_db.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1195"/>
+  <dimension ref="A1:H1196"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -31466,6 +31466,32 @@
         <v>53600</v>
       </c>
     </row>
+    <row r="1196" spans="1:8">
+      <c r="A1196" s="1">
+        <v>1194</v>
+      </c>
+      <c r="B1196" s="2">
+        <v>46286</v>
+      </c>
+      <c r="C1196">
+        <v>3262.5</v>
+      </c>
+      <c r="D1196">
+        <v>14788</v>
+      </c>
+      <c r="E1196">
+        <v>1890</v>
+      </c>
+      <c r="F1196">
+        <v>16125</v>
+      </c>
+      <c r="G1196">
+        <v>4018</v>
+      </c>
+      <c r="H1196">
+        <v>53785</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/westmetall/data/LME_westmetall_db.xlsx
+++ b/LME/parser/westmetall/data/LME_westmetall_db.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1196"/>
+  <dimension ref="A1:H1197"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -31492,6 +31492,32 @@
         <v>53785</v>
       </c>
     </row>
+    <row r="1197" spans="1:8">
+      <c r="A1197" s="1">
+        <v>1195</v>
+      </c>
+      <c r="B1197" s="2">
+        <v>46287</v>
+      </c>
+      <c r="C1197">
+        <v>3242</v>
+      </c>
+      <c r="D1197">
+        <v>14797</v>
+      </c>
+      <c r="E1197">
+        <v>1909</v>
+      </c>
+      <c r="F1197">
+        <v>16410</v>
+      </c>
+      <c r="G1197">
+        <v>4006</v>
+      </c>
+      <c r="H1197">
+        <v>53745</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/westmetall/data/LME_westmetall_db.xlsx
+++ b/LME/parser/westmetall/data/LME_westmetall_db.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1197"/>
+  <dimension ref="A1:H1198"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -31518,6 +31518,32 @@
         <v>53745</v>
       </c>
     </row>
+    <row r="1198" spans="1:8">
+      <c r="A1198" s="1">
+        <v>1196</v>
+      </c>
+      <c r="B1198" s="2">
+        <v>46288</v>
+      </c>
+      <c r="C1198">
+        <v>3240</v>
+      </c>
+      <c r="D1198">
+        <v>14735</v>
+      </c>
+      <c r="E1198">
+        <v>1885.5</v>
+      </c>
+      <c r="F1198">
+        <v>16430</v>
+      </c>
+      <c r="G1198">
+        <v>3949</v>
+      </c>
+      <c r="H1198">
+        <v>54050</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/westmetall/data/LME_westmetall_db.xlsx
+++ b/LME/parser/westmetall/data/LME_westmetall_db.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1198"/>
+  <dimension ref="A1:H1199"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -31544,6 +31544,32 @@
         <v>54050</v>
       </c>
     </row>
+    <row r="1199" spans="1:8">
+      <c r="A1199" s="1">
+        <v>1197</v>
+      </c>
+      <c r="B1199" s="2">
+        <v>46289</v>
+      </c>
+      <c r="C1199">
+        <v>3228</v>
+      </c>
+      <c r="D1199">
+        <v>14765</v>
+      </c>
+      <c r="E1199">
+        <v>1900</v>
+      </c>
+      <c r="F1199">
+        <v>16320</v>
+      </c>
+      <c r="G1199">
+        <v>3981</v>
+      </c>
+      <c r="H1199">
+        <v>53875</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/westmetall/data/LME_westmetall_db.xlsx
+++ b/LME/parser/westmetall/data/LME_westmetall_db.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1199"/>
+  <dimension ref="A1:H1200"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -31570,6 +31570,32 @@
         <v>53875</v>
       </c>
     </row>
+    <row r="1200" spans="1:8">
+      <c r="A1200" s="1">
+        <v>1198</v>
+      </c>
+      <c r="B1200" s="2">
+        <v>46290</v>
+      </c>
+      <c r="C1200">
+        <v>3254</v>
+      </c>
+      <c r="D1200">
+        <v>14740</v>
+      </c>
+      <c r="E1200">
+        <v>1902.5</v>
+      </c>
+      <c r="F1200">
+        <v>16050</v>
+      </c>
+      <c r="G1200">
+        <v>4060</v>
+      </c>
+      <c r="H1200">
+        <v>54025</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/westmetall/data/LME_westmetall_db.xlsx
+++ b/LME/parser/westmetall/data/LME_westmetall_db.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1200"/>
+  <dimension ref="A1:H1201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -31596,6 +31596,32 @@
         <v>54025</v>
       </c>
     </row>
+    <row r="1201" spans="1:8">
+      <c r="A1201" s="1">
+        <v>1199</v>
+      </c>
+      <c r="B1201" s="2">
+        <v>46293</v>
+      </c>
+      <c r="C1201">
+        <v>3248.5</v>
+      </c>
+      <c r="D1201">
+        <v>14544.5</v>
+      </c>
+      <c r="E1201">
+        <v>1886</v>
+      </c>
+      <c r="F1201">
+        <v>16050</v>
+      </c>
+      <c r="G1201">
+        <v>3957</v>
+      </c>
+      <c r="H1201">
+        <v>53750</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/westmetall/data/LME_westmetall_db.xlsx
+++ b/LME/parser/westmetall/data/LME_westmetall_db.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1201"/>
+  <dimension ref="A1:H1202"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -31622,6 +31622,32 @@
         <v>53750</v>
       </c>
     </row>
+    <row r="1202" spans="1:8">
+      <c r="A1202" s="1">
+        <v>1200</v>
+      </c>
+      <c r="B1202" s="2">
+        <v>46294</v>
+      </c>
+      <c r="C1202">
+        <v>3225.5</v>
+      </c>
+      <c r="D1202">
+        <v>14474.5</v>
+      </c>
+      <c r="E1202">
+        <v>1876</v>
+      </c>
+      <c r="F1202">
+        <v>15860</v>
+      </c>
+      <c r="G1202">
+        <v>3977</v>
+      </c>
+      <c r="H1202">
+        <v>53950</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/westmetall/data/LME_westmetall_db.xlsx
+++ b/LME/parser/westmetall/data/LME_westmetall_db.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1202"/>
+  <dimension ref="A1:H1203"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -31648,6 +31648,32 @@
         <v>53950</v>
       </c>
     </row>
+    <row r="1203" spans="1:8">
+      <c r="A1203" s="1">
+        <v>1201</v>
+      </c>
+      <c r="B1203" s="2">
+        <v>46295</v>
+      </c>
+      <c r="C1203">
+        <v>3204</v>
+      </c>
+      <c r="D1203">
+        <v>14487</v>
+      </c>
+      <c r="E1203">
+        <v>1856</v>
+      </c>
+      <c r="F1203">
+        <v>15860</v>
+      </c>
+      <c r="G1203">
+        <v>3954</v>
+      </c>
+      <c r="H1203">
+        <v>54075</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/westmetall/data/LME_westmetall_db.xlsx
+++ b/LME/parser/westmetall/data/LME_westmetall_db.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1203"/>
+  <dimension ref="A1:H1202"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -29651,25 +29651,25 @@
         <v>1124</v>
       </c>
       <c r="B1126" s="2">
-        <v>46186</v>
+        <v>46188</v>
       </c>
       <c r="C1126">
-        <v>3536</v>
+        <v>3419.5</v>
       </c>
       <c r="D1126">
-        <v>13603</v>
+        <v>13714</v>
       </c>
       <c r="E1126">
-        <v>1957</v>
+        <v>1964</v>
       </c>
       <c r="F1126">
-        <v>17630</v>
+        <v>17810</v>
       </c>
       <c r="G1126">
-        <v>3557</v>
+        <v>3562</v>
       </c>
       <c r="H1126">
-        <v>53350</v>
+        <v>54650</v>
       </c>
     </row>
     <row r="1127" spans="1:8">
@@ -29677,25 +29677,25 @@
         <v>1125</v>
       </c>
       <c r="B1127" s="2">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="C1127">
-        <v>3419.5</v>
+        <v>3359</v>
       </c>
       <c r="D1127">
-        <v>13714</v>
+        <v>13682</v>
       </c>
       <c r="E1127">
-        <v>1964</v>
+        <v>1956</v>
       </c>
       <c r="F1127">
-        <v>17810</v>
+        <v>17630</v>
       </c>
       <c r="G1127">
-        <v>3562</v>
+        <v>3550</v>
       </c>
       <c r="H1127">
-        <v>54650</v>
+        <v>55150</v>
       </c>
     </row>
     <row r="1128" spans="1:8">
@@ -29703,25 +29703,25 @@
         <v>1126</v>
       </c>
       <c r="B1128" s="2">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C1128">
-        <v>3359</v>
+        <v>3405.5</v>
       </c>
       <c r="D1128">
-        <v>13682</v>
+        <v>13736</v>
       </c>
       <c r="E1128">
-        <v>1956</v>
+        <v>1945</v>
       </c>
       <c r="F1128">
-        <v>17630</v>
+        <v>17820</v>
       </c>
       <c r="G1128">
-        <v>3550</v>
+        <v>3592</v>
       </c>
       <c r="H1128">
-        <v>55150</v>
+        <v>55400</v>
       </c>
     </row>
     <row r="1129" spans="1:8">
@@ -29729,25 +29729,25 @@
         <v>1127</v>
       </c>
       <c r="B1129" s="2">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="C1129">
-        <v>3405.5</v>
+        <v>3402</v>
       </c>
       <c r="D1129">
-        <v>13736</v>
+        <v>13612</v>
       </c>
       <c r="E1129">
         <v>1945</v>
       </c>
       <c r="F1129">
-        <v>17820</v>
+        <v>17770</v>
       </c>
       <c r="G1129">
-        <v>3592</v>
+        <v>3565</v>
       </c>
       <c r="H1129">
-        <v>55400</v>
+        <v>53455</v>
       </c>
     </row>
     <row r="1130" spans="1:8">
@@ -29755,25 +29755,25 @@
         <v>1128</v>
       </c>
       <c r="B1130" s="2">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="C1130">
-        <v>3402</v>
+        <v>3400</v>
       </c>
       <c r="D1130">
-        <v>13612</v>
+        <v>13530.5</v>
       </c>
       <c r="E1130">
-        <v>1945</v>
+        <v>1935</v>
       </c>
       <c r="F1130">
-        <v>17770</v>
+        <v>17590</v>
       </c>
       <c r="G1130">
-        <v>3565</v>
+        <v>3584.5</v>
       </c>
       <c r="H1130">
-        <v>53455</v>
+        <v>53200</v>
       </c>
     </row>
     <row r="1131" spans="1:8">
@@ -29781,25 +29781,25 @@
         <v>1129</v>
       </c>
       <c r="B1131" s="2">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="C1131">
-        <v>3400</v>
+        <v>3405</v>
       </c>
       <c r="D1131">
-        <v>13530.5</v>
+        <v>13642</v>
       </c>
       <c r="E1131">
-        <v>1935</v>
+        <v>1928.5</v>
       </c>
       <c r="F1131">
-        <v>17590</v>
+        <v>17640</v>
       </c>
       <c r="G1131">
-        <v>3584.5</v>
+        <v>3612.5</v>
       </c>
       <c r="H1131">
-        <v>53200</v>
+        <v>54995</v>
       </c>
     </row>
     <row r="1132" spans="1:8">
@@ -29807,25 +29807,25 @@
         <v>1130</v>
       </c>
       <c r="B1132" s="2">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="C1132">
-        <v>3405</v>
+        <v>3263.5</v>
       </c>
       <c r="D1132">
-        <v>13642</v>
+        <v>13334</v>
       </c>
       <c r="E1132">
-        <v>1928.5</v>
+        <v>1910</v>
       </c>
       <c r="F1132">
-        <v>17640</v>
+        <v>17105</v>
       </c>
       <c r="G1132">
-        <v>3612.5</v>
+        <v>3503</v>
       </c>
       <c r="H1132">
-        <v>54995</v>
+        <v>51900</v>
       </c>
     </row>
     <row r="1133" spans="1:8">
@@ -29833,25 +29833,25 @@
         <v>1131</v>
       </c>
       <c r="B1133" s="2">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="C1133">
-        <v>3263.5</v>
+        <v>3150</v>
       </c>
       <c r="D1133">
-        <v>13334</v>
+        <v>13181.5</v>
       </c>
       <c r="E1133">
-        <v>1910</v>
+        <v>1896</v>
       </c>
       <c r="F1133">
-        <v>17105</v>
+        <v>16610</v>
       </c>
       <c r="G1133">
-        <v>3503</v>
+        <v>3437</v>
       </c>
       <c r="H1133">
-        <v>51900</v>
+        <v>49550</v>
       </c>
     </row>
     <row r="1134" spans="1:8">
@@ -29859,25 +29859,25 @@
         <v>1132</v>
       </c>
       <c r="B1134" s="2">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="C1134">
-        <v>3150</v>
+        <v>3132</v>
       </c>
       <c r="D1134">
-        <v>13181.5</v>
+        <v>13194</v>
       </c>
       <c r="E1134">
-        <v>1896</v>
+        <v>1894</v>
       </c>
       <c r="F1134">
-        <v>16610</v>
+        <v>16660</v>
       </c>
       <c r="G1134">
-        <v>3437</v>
+        <v>3432</v>
       </c>
       <c r="H1134">
-        <v>49550</v>
+        <v>50100</v>
       </c>
     </row>
     <row r="1135" spans="1:8">
@@ -29885,25 +29885,25 @@
         <v>1133</v>
       </c>
       <c r="B1135" s="2">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="C1135">
-        <v>3132</v>
+        <v>3164</v>
       </c>
       <c r="D1135">
-        <v>13194</v>
+        <v>13287</v>
       </c>
       <c r="E1135">
-        <v>1894</v>
+        <v>1880</v>
       </c>
       <c r="F1135">
-        <v>16660</v>
+        <v>16570</v>
       </c>
       <c r="G1135">
-        <v>3432</v>
+        <v>3460</v>
       </c>
       <c r="H1135">
-        <v>50100</v>
+        <v>50325</v>
       </c>
     </row>
     <row r="1136" spans="1:8">
@@ -29911,25 +29911,25 @@
         <v>1134</v>
       </c>
       <c r="B1136" s="2">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="C1136">
-        <v>3164</v>
+        <v>3160.5</v>
       </c>
       <c r="D1136">
-        <v>13287</v>
+        <v>13302.5</v>
       </c>
       <c r="E1136">
-        <v>1880</v>
+        <v>1871.5</v>
       </c>
       <c r="F1136">
-        <v>16570</v>
+        <v>16455</v>
       </c>
       <c r="G1136">
-        <v>3460</v>
+        <v>3491</v>
       </c>
       <c r="H1136">
-        <v>50325</v>
+        <v>51000</v>
       </c>
     </row>
     <row r="1137" spans="1:8">
@@ -29937,25 +29937,25 @@
         <v>1135</v>
       </c>
       <c r="B1137" s="2">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="C1137">
-        <v>3160.5</v>
+        <v>3105.5</v>
       </c>
       <c r="D1137">
-        <v>13302.5</v>
+        <v>13341</v>
       </c>
       <c r="E1137">
-        <v>1871.5</v>
+        <v>1845</v>
       </c>
       <c r="F1137">
-        <v>16455</v>
+        <v>16275</v>
       </c>
       <c r="G1137">
-        <v>3491</v>
+        <v>3565.5</v>
       </c>
       <c r="H1137">
-        <v>51000</v>
+        <v>51100</v>
       </c>
     </row>
     <row r="1138" spans="1:8">
@@ -29963,25 +29963,25 @@
         <v>1136</v>
       </c>
       <c r="B1138" s="2">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="C1138">
-        <v>3105.5</v>
+        <v>3075</v>
       </c>
       <c r="D1138">
-        <v>13341</v>
+        <v>13170</v>
       </c>
       <c r="E1138">
-        <v>1845</v>
+        <v>1840</v>
       </c>
       <c r="F1138">
-        <v>16275</v>
+        <v>16175</v>
       </c>
       <c r="G1138">
-        <v>3565.5</v>
+        <v>3529</v>
       </c>
       <c r="H1138">
-        <v>51100</v>
+        <v>51150</v>
       </c>
     </row>
     <row r="1139" spans="1:8">
@@ -29989,25 +29989,25 @@
         <v>1137</v>
       </c>
       <c r="B1139" s="2">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="C1139">
-        <v>3075</v>
+        <v>3061.5</v>
       </c>
       <c r="D1139">
-        <v>13170</v>
+        <v>13202</v>
       </c>
       <c r="E1139">
-        <v>1840</v>
+        <v>1828.5</v>
       </c>
       <c r="F1139">
-        <v>16175</v>
+        <v>16070</v>
       </c>
       <c r="G1139">
-        <v>3529</v>
+        <v>3475</v>
       </c>
       <c r="H1139">
-        <v>51150</v>
+        <v>51200</v>
       </c>
     </row>
     <row r="1140" spans="1:8">
@@ -30015,25 +30015,25 @@
         <v>1138</v>
       </c>
       <c r="B1140" s="2">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="C1140">
-        <v>3061.5</v>
+        <v>3080</v>
       </c>
       <c r="D1140">
-        <v>13202</v>
+        <v>13298.5</v>
       </c>
       <c r="E1140">
-        <v>1828.5</v>
+        <v>1851</v>
       </c>
       <c r="F1140">
-        <v>16070</v>
+        <v>16115</v>
       </c>
       <c r="G1140">
-        <v>3475</v>
+        <v>3546</v>
       </c>
       <c r="H1140">
-        <v>51200</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="1141" spans="1:8">
@@ -30041,25 +30041,25 @@
         <v>1139</v>
       </c>
       <c r="B1141" s="2">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="C1141">
-        <v>3080</v>
+        <v>3105</v>
       </c>
       <c r="D1141">
-        <v>13298.5</v>
+        <v>13310</v>
       </c>
       <c r="E1141">
-        <v>1851</v>
+        <v>1852.5</v>
       </c>
       <c r="F1141">
-        <v>16115</v>
+        <v>16065</v>
       </c>
       <c r="G1141">
-        <v>3546</v>
+        <v>3599</v>
       </c>
       <c r="H1141">
-        <v>52000</v>
+        <v>52525</v>
       </c>
     </row>
     <row r="1142" spans="1:8">
@@ -30067,25 +30067,25 @@
         <v>1140</v>
       </c>
       <c r="B1142" s="2">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="C1142">
-        <v>3105</v>
+        <v>3119</v>
       </c>
       <c r="D1142">
-        <v>13310</v>
+        <v>13309</v>
       </c>
       <c r="E1142">
-        <v>1852.5</v>
+        <v>1849</v>
       </c>
       <c r="F1142">
-        <v>16065</v>
+        <v>16160</v>
       </c>
       <c r="G1142">
-        <v>3599</v>
+        <v>3560</v>
       </c>
       <c r="H1142">
-        <v>52525</v>
+        <v>52900</v>
       </c>
     </row>
     <row r="1143" spans="1:8">
@@ -30093,25 +30093,25 @@
         <v>1141</v>
       </c>
       <c r="B1143" s="2">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="C1143">
-        <v>3119</v>
+        <v>3141</v>
       </c>
       <c r="D1143">
-        <v>13309</v>
+        <v>13090</v>
       </c>
       <c r="E1143">
-        <v>1849</v>
+        <v>1851</v>
       </c>
       <c r="F1143">
         <v>16160</v>
       </c>
       <c r="G1143">
-        <v>3560</v>
+        <v>3529</v>
       </c>
       <c r="H1143">
-        <v>52900</v>
+        <v>52350</v>
       </c>
     </row>
     <row r="1144" spans="1:8">
@@ -30119,25 +30119,25 @@
         <v>1142</v>
       </c>
       <c r="B1144" s="2">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="C1144">
-        <v>3141</v>
+        <v>3164</v>
       </c>
       <c r="D1144">
-        <v>13090</v>
+        <v>13356.5</v>
       </c>
       <c r="E1144">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="F1144">
-        <v>16160</v>
+        <v>16355</v>
       </c>
       <c r="G1144">
-        <v>3529</v>
+        <v>3622</v>
       </c>
       <c r="H1144">
-        <v>52350</v>
+        <v>53450</v>
       </c>
     </row>
     <row r="1145" spans="1:8">
@@ -30145,25 +30145,25 @@
         <v>1143</v>
       </c>
       <c r="B1145" s="2">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="C1145">
-        <v>3164</v>
+        <v>3156</v>
       </c>
       <c r="D1145">
-        <v>13356.5</v>
+        <v>13408.5</v>
       </c>
       <c r="E1145">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="F1145">
-        <v>16355</v>
+        <v>16410</v>
       </c>
       <c r="G1145">
-        <v>3622</v>
+        <v>3602</v>
       </c>
       <c r="H1145">
-        <v>53450</v>
+        <v>52575</v>
       </c>
     </row>
     <row r="1146" spans="1:8">
@@ -30171,25 +30171,25 @@
         <v>1144</v>
       </c>
       <c r="B1146" s="2">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="C1146">
-        <v>3156</v>
+        <v>3138.5</v>
       </c>
       <c r="D1146">
-        <v>13408.5</v>
+        <v>13460.5</v>
       </c>
       <c r="E1146">
-        <v>1851</v>
+        <v>1832</v>
       </c>
       <c r="F1146">
-        <v>16410</v>
+        <v>16405</v>
       </c>
       <c r="G1146">
-        <v>3602</v>
+        <v>3571</v>
       </c>
       <c r="H1146">
-        <v>52575</v>
+        <v>52705</v>
       </c>
     </row>
     <row r="1147" spans="1:8">
@@ -30197,25 +30197,25 @@
         <v>1145</v>
       </c>
       <c r="B1147" s="2">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="C1147">
-        <v>3138.5</v>
+        <v>3171</v>
       </c>
       <c r="D1147">
-        <v>13460.5</v>
+        <v>13541</v>
       </c>
       <c r="E1147">
-        <v>1832</v>
+        <v>1803</v>
       </c>
       <c r="F1147">
-        <v>16405</v>
+        <v>16590</v>
       </c>
       <c r="G1147">
-        <v>3571</v>
+        <v>3589.5</v>
       </c>
       <c r="H1147">
-        <v>52705</v>
+        <v>53900</v>
       </c>
     </row>
     <row r="1148" spans="1:8">
@@ -30223,25 +30223,25 @@
         <v>1146</v>
       </c>
       <c r="B1148" s="2">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="C1148">
-        <v>3171</v>
+        <v>3153.5</v>
       </c>
       <c r="D1148">
-        <v>13541</v>
+        <v>13537</v>
       </c>
       <c r="E1148">
-        <v>1803</v>
+        <v>1797</v>
       </c>
       <c r="F1148">
-        <v>16590</v>
+        <v>16505</v>
       </c>
       <c r="G1148">
-        <v>3589.5</v>
+        <v>3553.5</v>
       </c>
       <c r="H1148">
-        <v>53900</v>
+        <v>52705</v>
       </c>
     </row>
     <row r="1149" spans="1:8">
@@ -30249,25 +30249,25 @@
         <v>1147</v>
       </c>
       <c r="B1149" s="2">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="C1149">
-        <v>3153.5</v>
+        <v>3170</v>
       </c>
       <c r="D1149">
-        <v>13537</v>
+        <v>13565</v>
       </c>
       <c r="E1149">
-        <v>1797</v>
+        <v>1827.5</v>
       </c>
       <c r="F1149">
-        <v>16505</v>
+        <v>17150</v>
       </c>
       <c r="G1149">
-        <v>3553.5</v>
+        <v>3591</v>
       </c>
       <c r="H1149">
-        <v>52705</v>
+        <v>52860</v>
       </c>
     </row>
     <row r="1150" spans="1:8">
@@ -30275,25 +30275,25 @@
         <v>1148</v>
       </c>
       <c r="B1150" s="2">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="C1150">
-        <v>3170</v>
+        <v>3154</v>
       </c>
       <c r="D1150">
-        <v>13565</v>
+        <v>13373.5</v>
       </c>
       <c r="E1150">
-        <v>1827.5</v>
+        <v>1821</v>
       </c>
       <c r="F1150">
-        <v>17150</v>
+        <v>16725</v>
       </c>
       <c r="G1150">
-        <v>3591</v>
+        <v>3549</v>
       </c>
       <c r="H1150">
-        <v>52860</v>
+        <v>52045</v>
       </c>
     </row>
     <row r="1151" spans="1:8">
@@ -30301,25 +30301,25 @@
         <v>1149</v>
       </c>
       <c r="B1151" s="2">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="C1151">
-        <v>3154</v>
+        <v>3156</v>
       </c>
       <c r="D1151">
-        <v>13373.5</v>
+        <v>13629</v>
       </c>
       <c r="E1151">
-        <v>1821</v>
+        <v>1830</v>
       </c>
       <c r="F1151">
-        <v>16725</v>
+        <v>16850</v>
       </c>
       <c r="G1151">
-        <v>3549</v>
+        <v>3575</v>
       </c>
       <c r="H1151">
-        <v>52045</v>
+        <v>53300</v>
       </c>
     </row>
     <row r="1152" spans="1:8">
@@ -30327,25 +30327,25 @@
         <v>1150</v>
       </c>
       <c r="B1152" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="C1152">
-        <v>3156</v>
+        <v>3183.5</v>
       </c>
       <c r="D1152">
-        <v>13629</v>
+        <v>13856</v>
       </c>
       <c r="E1152">
-        <v>1830</v>
+        <v>1842</v>
       </c>
       <c r="F1152">
-        <v>16850</v>
+        <v>16970</v>
       </c>
       <c r="G1152">
-        <v>3575</v>
+        <v>3591</v>
       </c>
       <c r="H1152">
-        <v>53300</v>
+        <v>54100</v>
       </c>
     </row>
     <row r="1153" spans="1:8">
@@ -30353,25 +30353,25 @@
         <v>1151</v>
       </c>
       <c r="B1153" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="C1153">
-        <v>3183.5</v>
+        <v>3205</v>
       </c>
       <c r="D1153">
-        <v>13856</v>
+        <v>13895</v>
       </c>
       <c r="E1153">
-        <v>1842</v>
+        <v>1841.5</v>
       </c>
       <c r="F1153">
-        <v>16970</v>
+        <v>16940</v>
       </c>
       <c r="G1153">
-        <v>3591</v>
+        <v>3614</v>
       </c>
       <c r="H1153">
-        <v>54100</v>
+        <v>53900</v>
       </c>
     </row>
     <row r="1154" spans="1:8">
@@ -30379,25 +30379,25 @@
         <v>1152</v>
       </c>
       <c r="B1154" s="2">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C1154">
-        <v>3205</v>
+        <v>3194</v>
       </c>
       <c r="D1154">
-        <v>13895</v>
+        <v>13745</v>
       </c>
       <c r="E1154">
-        <v>1841.5</v>
+        <v>1875</v>
       </c>
       <c r="F1154">
-        <v>16940</v>
+        <v>17200</v>
       </c>
       <c r="G1154">
-        <v>3614</v>
+        <v>3653</v>
       </c>
       <c r="H1154">
-        <v>53900</v>
+        <v>53800</v>
       </c>
     </row>
     <row r="1155" spans="1:8">
@@ -30405,25 +30405,25 @@
         <v>1153</v>
       </c>
       <c r="B1155" s="2">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="C1155">
-        <v>3194</v>
+        <v>3175</v>
       </c>
       <c r="D1155">
-        <v>13745</v>
+        <v>13617</v>
       </c>
       <c r="E1155">
-        <v>1875</v>
+        <v>1865.5</v>
       </c>
       <c r="F1155">
-        <v>17200</v>
+        <v>17205</v>
       </c>
       <c r="G1155">
-        <v>3653</v>
+        <v>3633</v>
       </c>
       <c r="H1155">
-        <v>53800</v>
+        <v>53250</v>
       </c>
     </row>
     <row r="1156" spans="1:8">
@@ -30431,25 +30431,25 @@
         <v>1154</v>
       </c>
       <c r="B1156" s="2">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="C1156">
-        <v>3175</v>
+        <v>3192</v>
       </c>
       <c r="D1156">
-        <v>13617</v>
+        <v>13810</v>
       </c>
       <c r="E1156">
-        <v>1865.5</v>
+        <v>1859</v>
       </c>
       <c r="F1156">
-        <v>17205</v>
+        <v>17165</v>
       </c>
       <c r="G1156">
-        <v>3633</v>
+        <v>3685.5</v>
       </c>
       <c r="H1156">
-        <v>53250</v>
+        <v>54250</v>
       </c>
     </row>
     <row r="1157" spans="1:8">
@@ -30457,25 +30457,25 @@
         <v>1155</v>
       </c>
       <c r="B1157" s="2">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="C1157">
-        <v>3192</v>
+        <v>3159.5</v>
       </c>
       <c r="D1157">
-        <v>13810</v>
+        <v>13643.5</v>
       </c>
       <c r="E1157">
-        <v>1859</v>
+        <v>1856</v>
       </c>
       <c r="F1157">
-        <v>17165</v>
+        <v>16860</v>
       </c>
       <c r="G1157">
-        <v>3685.5</v>
+        <v>3631.5</v>
       </c>
       <c r="H1157">
-        <v>54250</v>
+        <v>53600</v>
       </c>
     </row>
     <row r="1158" spans="1:8">
@@ -30483,25 +30483,25 @@
         <v>1156</v>
       </c>
       <c r="B1158" s="2">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C1158">
-        <v>3159.5</v>
+        <v>3207</v>
       </c>
       <c r="D1158">
-        <v>13643.5</v>
+        <v>13633</v>
       </c>
       <c r="E1158">
-        <v>1856</v>
+        <v>1877</v>
       </c>
       <c r="F1158">
-        <v>16860</v>
+        <v>17000</v>
       </c>
       <c r="G1158">
-        <v>3631.5</v>
+        <v>3639</v>
       </c>
       <c r="H1158">
-        <v>53600</v>
+        <v>53990</v>
       </c>
     </row>
     <row r="1159" spans="1:8">
@@ -30509,25 +30509,25 @@
         <v>1157</v>
       </c>
       <c r="B1159" s="2">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C1159">
-        <v>3207</v>
+        <v>3231</v>
       </c>
       <c r="D1159">
-        <v>13633</v>
+        <v>13795</v>
       </c>
       <c r="E1159">
-        <v>1877</v>
+        <v>1863</v>
       </c>
       <c r="F1159">
-        <v>17000</v>
+        <v>16945</v>
       </c>
       <c r="G1159">
-        <v>3639</v>
+        <v>3662</v>
       </c>
       <c r="H1159">
-        <v>53990</v>
+        <v>54125</v>
       </c>
     </row>
     <row r="1160" spans="1:8">
@@ -30535,25 +30535,25 @@
         <v>1158</v>
       </c>
       <c r="B1160" s="2">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="C1160">
-        <v>3231</v>
+        <v>3196</v>
       </c>
       <c r="D1160">
-        <v>13795</v>
+        <v>13834</v>
       </c>
       <c r="E1160">
-        <v>1863</v>
+        <v>1851.5</v>
       </c>
       <c r="F1160">
-        <v>16945</v>
+        <v>17100</v>
       </c>
       <c r="G1160">
-        <v>3662</v>
+        <v>3710.5</v>
       </c>
       <c r="H1160">
-        <v>54125</v>
+        <v>54660</v>
       </c>
     </row>
     <row r="1161" spans="1:8">
@@ -30561,25 +30561,25 @@
         <v>1159</v>
       </c>
       <c r="B1161" s="2">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="C1161">
-        <v>3196</v>
+        <v>3260</v>
       </c>
       <c r="D1161">
-        <v>13834</v>
+        <v>13945</v>
       </c>
       <c r="E1161">
-        <v>1851.5</v>
+        <v>1828</v>
       </c>
       <c r="F1161">
-        <v>17100</v>
+        <v>16785</v>
       </c>
       <c r="G1161">
-        <v>3710.5</v>
+        <v>3751</v>
       </c>
       <c r="H1161">
-        <v>54660</v>
+        <v>55200</v>
       </c>
     </row>
     <row r="1162" spans="1:8">
@@ -30587,25 +30587,25 @@
         <v>1160</v>
       </c>
       <c r="B1162" s="2">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C1162">
-        <v>3260</v>
+        <v>3271</v>
       </c>
       <c r="D1162">
-        <v>13945</v>
+        <v>14195</v>
       </c>
       <c r="E1162">
-        <v>1828</v>
+        <v>1847</v>
       </c>
       <c r="F1162">
-        <v>16785</v>
+        <v>17125</v>
       </c>
       <c r="G1162">
-        <v>3751</v>
+        <v>3730</v>
       </c>
       <c r="H1162">
-        <v>55200</v>
+        <v>55700</v>
       </c>
     </row>
     <row r="1163" spans="1:8">
@@ -30613,25 +30613,25 @@
         <v>1161</v>
       </c>
       <c r="B1163" s="2">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C1163">
-        <v>3271</v>
+        <v>3229</v>
       </c>
       <c r="D1163">
-        <v>14195</v>
+        <v>14167.5</v>
       </c>
       <c r="E1163">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="F1163">
-        <v>17125</v>
+        <v>16915</v>
       </c>
       <c r="G1163">
-        <v>3730</v>
+        <v>3737</v>
       </c>
       <c r="H1163">
-        <v>55700</v>
+        <v>56225</v>
       </c>
     </row>
     <row r="1164" spans="1:8">
@@ -30639,25 +30639,25 @@
         <v>1162</v>
       </c>
       <c r="B1164" s="2">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C1164">
-        <v>3229</v>
+        <v>3261</v>
       </c>
       <c r="D1164">
-        <v>14167.5</v>
+        <v>14455</v>
       </c>
       <c r="E1164">
-        <v>1845</v>
+        <v>1851</v>
       </c>
       <c r="F1164">
-        <v>16915</v>
+        <v>16595</v>
       </c>
       <c r="G1164">
-        <v>3737</v>
+        <v>3857</v>
       </c>
       <c r="H1164">
-        <v>56225</v>
+        <v>56500</v>
       </c>
     </row>
     <row r="1165" spans="1:8">
@@ -30665,25 +30665,25 @@
         <v>1163</v>
       </c>
       <c r="B1165" s="2">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C1165">
-        <v>3261</v>
+        <v>3279.5</v>
       </c>
       <c r="D1165">
-        <v>14455</v>
+        <v>14240</v>
       </c>
       <c r="E1165">
-        <v>1851</v>
+        <v>1840.5</v>
       </c>
       <c r="F1165">
-        <v>16595</v>
+        <v>16745</v>
       </c>
       <c r="G1165">
-        <v>3857</v>
+        <v>3785</v>
       </c>
       <c r="H1165">
-        <v>56500</v>
+        <v>56100</v>
       </c>
     </row>
     <row r="1166" spans="1:8">
@@ -30691,25 +30691,25 @@
         <v>1164</v>
       </c>
       <c r="B1166" s="2">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="C1166">
-        <v>3279.5</v>
+        <v>3327.5</v>
       </c>
       <c r="D1166">
-        <v>14240</v>
+        <v>14290</v>
       </c>
       <c r="E1166">
-        <v>1840.5</v>
+        <v>1858</v>
       </c>
       <c r="F1166">
-        <v>16745</v>
+        <v>16775</v>
       </c>
       <c r="G1166">
-        <v>3785</v>
+        <v>3786</v>
       </c>
       <c r="H1166">
-        <v>56100</v>
+        <v>55900</v>
       </c>
     </row>
     <row r="1167" spans="1:8">
@@ -30717,25 +30717,25 @@
         <v>1165</v>
       </c>
       <c r="B1167" s="2">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="C1167">
-        <v>3327.5</v>
+        <v>3373</v>
       </c>
       <c r="D1167">
-        <v>14290</v>
+        <v>14424.5</v>
       </c>
       <c r="E1167">
-        <v>1858</v>
+        <v>1878</v>
       </c>
       <c r="F1167">
-        <v>16775</v>
+        <v>16640</v>
       </c>
       <c r="G1167">
-        <v>3786</v>
+        <v>3822</v>
       </c>
       <c r="H1167">
-        <v>55900</v>
+        <v>55305</v>
       </c>
     </row>
     <row r="1168" spans="1:8">
@@ -30743,25 +30743,25 @@
         <v>1166</v>
       </c>
       <c r="B1168" s="2">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="C1168">
-        <v>3373</v>
+        <v>3307.5</v>
       </c>
       <c r="D1168">
-        <v>14424.5</v>
+        <v>14376</v>
       </c>
       <c r="E1168">
-        <v>1878</v>
+        <v>1880</v>
       </c>
       <c r="F1168">
-        <v>16640</v>
+        <v>16725</v>
       </c>
       <c r="G1168">
-        <v>3822</v>
+        <v>3852</v>
       </c>
       <c r="H1168">
-        <v>55305</v>
+        <v>56050</v>
       </c>
     </row>
     <row r="1169" spans="1:8">
@@ -30769,25 +30769,25 @@
         <v>1167</v>
       </c>
       <c r="B1169" s="2">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="C1169">
-        <v>3307.5</v>
+        <v>3279</v>
       </c>
       <c r="D1169">
-        <v>14376</v>
+        <v>14285</v>
       </c>
       <c r="E1169">
-        <v>1880</v>
+        <v>1856</v>
       </c>
       <c r="F1169">
-        <v>16725</v>
+        <v>16690</v>
       </c>
       <c r="G1169">
-        <v>3852</v>
+        <v>3806</v>
       </c>
       <c r="H1169">
-        <v>56050</v>
+        <v>56150</v>
       </c>
     </row>
     <row r="1170" spans="1:8">
@@ -30795,25 +30795,25 @@
         <v>1168</v>
       </c>
       <c r="B1170" s="2">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="C1170">
-        <v>3279</v>
+        <v>3248</v>
       </c>
       <c r="D1170">
-        <v>14285</v>
+        <v>14545</v>
       </c>
       <c r="E1170">
-        <v>1856</v>
+        <v>1846</v>
       </c>
       <c r="F1170">
-        <v>16690</v>
+        <v>16575</v>
       </c>
       <c r="G1170">
-        <v>3806</v>
+        <v>3875</v>
       </c>
       <c r="H1170">
-        <v>56150</v>
+        <v>56075</v>
       </c>
     </row>
     <row r="1171" spans="1:8">
@@ -30821,25 +30821,25 @@
         <v>1169</v>
       </c>
       <c r="B1171" s="2">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="C1171">
-        <v>3248</v>
+        <v>3272</v>
       </c>
       <c r="D1171">
-        <v>14545</v>
+        <v>14850</v>
       </c>
       <c r="E1171">
-        <v>1846</v>
+        <v>1851.5</v>
       </c>
       <c r="F1171">
-        <v>16575</v>
+        <v>16670</v>
       </c>
       <c r="G1171">
-        <v>3875</v>
+        <v>3855</v>
       </c>
       <c r="H1171">
-        <v>56075</v>
+        <v>56225</v>
       </c>
     </row>
     <row r="1172" spans="1:8">
@@ -30847,25 +30847,25 @@
         <v>1170</v>
       </c>
       <c r="B1172" s="2">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="C1172">
-        <v>3272</v>
+        <v>3219</v>
       </c>
       <c r="D1172">
-        <v>14850</v>
+        <v>14335</v>
       </c>
       <c r="E1172">
-        <v>1851.5</v>
+        <v>1840.5</v>
       </c>
       <c r="F1172">
-        <v>16670</v>
+        <v>16740</v>
       </c>
       <c r="G1172">
-        <v>3855</v>
+        <v>3795</v>
       </c>
       <c r="H1172">
-        <v>56225</v>
+        <v>55550</v>
       </c>
     </row>
     <row r="1173" spans="1:8">
@@ -30873,25 +30873,25 @@
         <v>1171</v>
       </c>
       <c r="B1173" s="2">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="C1173">
-        <v>3219</v>
+        <v>3191.5</v>
       </c>
       <c r="D1173">
-        <v>14335</v>
+        <v>14180</v>
       </c>
       <c r="E1173">
-        <v>1840.5</v>
+        <v>1827</v>
       </c>
       <c r="F1173">
-        <v>16740</v>
+        <v>16690</v>
       </c>
       <c r="G1173">
-        <v>3795</v>
+        <v>3750</v>
       </c>
       <c r="H1173">
-        <v>55550</v>
+        <v>54375</v>
       </c>
     </row>
     <row r="1174" spans="1:8">
@@ -30899,25 +30899,25 @@
         <v>1172</v>
       </c>
       <c r="B1174" s="2">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="C1174">
-        <v>3191.5</v>
+        <v>3182</v>
       </c>
       <c r="D1174">
-        <v>14180</v>
+        <v>14170</v>
       </c>
       <c r="E1174">
-        <v>1827</v>
+        <v>1848</v>
       </c>
       <c r="F1174">
-        <v>16690</v>
+        <v>16660</v>
       </c>
       <c r="G1174">
-        <v>3750</v>
+        <v>3865.5</v>
       </c>
       <c r="H1174">
-        <v>54375</v>
+        <v>54850</v>
       </c>
     </row>
     <row r="1175" spans="1:8">
@@ -30925,25 +30925,25 @@
         <v>1173</v>
       </c>
       <c r="B1175" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C1175">
-        <v>3182</v>
+        <v>3227</v>
       </c>
       <c r="D1175">
-        <v>14170</v>
+        <v>14291</v>
       </c>
       <c r="E1175">
-        <v>1848</v>
+        <v>1857</v>
       </c>
       <c r="F1175">
-        <v>16660</v>
+        <v>16860</v>
       </c>
       <c r="G1175">
-        <v>3865.5</v>
+        <v>3980</v>
       </c>
       <c r="H1175">
-        <v>54850</v>
+        <v>55900</v>
       </c>
     </row>
     <row r="1176" spans="1:8">
@@ -30951,22 +30951,22 @@
         <v>1174</v>
       </c>
       <c r="B1176" s="2">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="C1176">
-        <v>3227</v>
+        <v>3215.5</v>
       </c>
       <c r="D1176">
-        <v>14291</v>
+        <v>14344</v>
       </c>
       <c r="E1176">
-        <v>1857</v>
+        <v>1862.5</v>
       </c>
       <c r="F1176">
-        <v>16860</v>
+        <v>16940</v>
       </c>
       <c r="G1176">
-        <v>3980</v>
+        <v>3985</v>
       </c>
       <c r="H1176">
         <v>55900</v>
@@ -30977,25 +30977,25 @@
         <v>1175</v>
       </c>
       <c r="B1177" s="2">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="C1177">
-        <v>3215.5</v>
+        <v>3188</v>
       </c>
       <c r="D1177">
-        <v>14344</v>
+        <v>14425</v>
       </c>
       <c r="E1177">
-        <v>1862.5</v>
+        <v>1867</v>
       </c>
       <c r="F1177">
-        <v>16940</v>
+        <v>16780</v>
       </c>
       <c r="G1177">
-        <v>3985</v>
+        <v>3987</v>
       </c>
       <c r="H1177">
-        <v>55900</v>
+        <v>55700</v>
       </c>
     </row>
     <row r="1178" spans="1:8">
@@ -31003,25 +31003,25 @@
         <v>1176</v>
       </c>
       <c r="B1178" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="C1178">
-        <v>3188</v>
+        <v>3227.5</v>
       </c>
       <c r="D1178">
-        <v>14425</v>
+        <v>14525</v>
       </c>
       <c r="E1178">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="F1178">
-        <v>16780</v>
+        <v>16895</v>
       </c>
       <c r="G1178">
-        <v>3987</v>
+        <v>4107</v>
       </c>
       <c r="H1178">
-        <v>55700</v>
+        <v>55300</v>
       </c>
     </row>
     <row r="1179" spans="1:8">
@@ -31029,25 +31029,25 @@
         <v>1177</v>
       </c>
       <c r="B1179" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="C1179">
-        <v>3227.5</v>
+        <v>3212.5</v>
       </c>
       <c r="D1179">
-        <v>14525</v>
+        <v>14490</v>
       </c>
       <c r="E1179">
-        <v>1866</v>
+        <v>1872</v>
       </c>
       <c r="F1179">
-        <v>16895</v>
+        <v>16660</v>
       </c>
       <c r="G1179">
         <v>4107</v>
       </c>
       <c r="H1179">
-        <v>55300</v>
+        <v>54950</v>
       </c>
     </row>
     <row r="1180" spans="1:8">
@@ -31055,25 +31055,25 @@
         <v>1178</v>
       </c>
       <c r="B1180" s="2">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C1180">
-        <v>3212.5</v>
+        <v>3222</v>
       </c>
       <c r="D1180">
-        <v>14490</v>
+        <v>14535</v>
       </c>
       <c r="E1180">
-        <v>1872</v>
+        <v>1880</v>
       </c>
       <c r="F1180">
-        <v>16660</v>
+        <v>16850</v>
       </c>
       <c r="G1180">
-        <v>4107</v>
+        <v>4070</v>
       </c>
       <c r="H1180">
-        <v>54950</v>
+        <v>55125</v>
       </c>
     </row>
     <row r="1181" spans="1:8">
@@ -31081,25 +31081,25 @@
         <v>1179</v>
       </c>
       <c r="B1181" s="2">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="C1181">
-        <v>3222</v>
+        <v>3261</v>
       </c>
       <c r="D1181">
-        <v>14535</v>
+        <v>14395.5</v>
       </c>
       <c r="E1181">
-        <v>1880</v>
+        <v>1874</v>
       </c>
       <c r="F1181">
-        <v>16850</v>
+        <v>16350</v>
       </c>
       <c r="G1181">
-        <v>4070</v>
+        <v>4115</v>
       </c>
       <c r="H1181">
-        <v>55125</v>
+        <v>54725</v>
       </c>
     </row>
     <row r="1182" spans="1:8">
@@ -31107,25 +31107,25 @@
         <v>1180</v>
       </c>
       <c r="B1182" s="2">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="C1182">
-        <v>3261</v>
+        <v>3255.5</v>
       </c>
       <c r="D1182">
-        <v>14395.5</v>
+        <v>14355</v>
       </c>
       <c r="E1182">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="F1182">
-        <v>16350</v>
+        <v>16530</v>
       </c>
       <c r="G1182">
-        <v>4115</v>
+        <v>4000</v>
       </c>
       <c r="H1182">
-        <v>54725</v>
+        <v>53950</v>
       </c>
     </row>
     <row r="1183" spans="1:8">
@@ -31133,25 +31133,25 @@
         <v>1181</v>
       </c>
       <c r="B1183" s="2">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="C1183">
-        <v>3255.5</v>
+        <v>3303</v>
       </c>
       <c r="D1183">
-        <v>14355</v>
+        <v>14359</v>
       </c>
       <c r="E1183">
-        <v>1873</v>
+        <v>1870</v>
       </c>
       <c r="F1183">
-        <v>16530</v>
+        <v>16615</v>
       </c>
       <c r="G1183">
-        <v>4000</v>
+        <v>3995.5</v>
       </c>
       <c r="H1183">
-        <v>53950</v>
+        <v>54450</v>
       </c>
     </row>
     <row r="1184" spans="1:8">
@@ -31159,25 +31159,25 @@
         <v>1182</v>
       </c>
       <c r="B1184" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="C1184">
-        <v>3303</v>
+        <v>3292.5</v>
       </c>
       <c r="D1184">
-        <v>14359</v>
+        <v>14371</v>
       </c>
       <c r="E1184">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="F1184">
-        <v>16615</v>
+        <v>16690</v>
       </c>
       <c r="G1184">
-        <v>3995.5</v>
+        <v>4087</v>
       </c>
       <c r="H1184">
-        <v>54450</v>
+        <v>54525</v>
       </c>
     </row>
     <row r="1185" spans="1:8">
@@ -31185,25 +31185,25 @@
         <v>1183</v>
       </c>
       <c r="B1185" s="2">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="C1185">
-        <v>3292.5</v>
+        <v>3310</v>
       </c>
       <c r="D1185">
-        <v>14371</v>
+        <v>14540</v>
       </c>
       <c r="E1185">
-        <v>1871</v>
+        <v>1875</v>
       </c>
       <c r="F1185">
-        <v>16690</v>
+        <v>16600</v>
       </c>
       <c r="G1185">
-        <v>4087</v>
+        <v>4157</v>
       </c>
       <c r="H1185">
-        <v>54525</v>
+        <v>55100</v>
       </c>
     </row>
     <row r="1186" spans="1:8">
@@ -31211,25 +31211,25 @@
         <v>1184</v>
       </c>
       <c r="B1186" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="C1186">
-        <v>3310</v>
+        <v>3325</v>
       </c>
       <c r="D1186">
-        <v>14540</v>
+        <v>14737</v>
       </c>
       <c r="E1186">
-        <v>1875</v>
+        <v>1859</v>
       </c>
       <c r="F1186">
-        <v>16600</v>
+        <v>16675</v>
       </c>
       <c r="G1186">
-        <v>4157</v>
+        <v>4110</v>
       </c>
       <c r="H1186">
-        <v>55100</v>
+        <v>54900</v>
       </c>
     </row>
     <row r="1187" spans="1:8">
@@ -31237,25 +31237,25 @@
         <v>1185</v>
       </c>
       <c r="B1187" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C1187">
-        <v>3325</v>
+        <v>3352</v>
       </c>
       <c r="D1187">
-        <v>14737</v>
+        <v>14672</v>
       </c>
       <c r="E1187">
-        <v>1859</v>
+        <v>1871</v>
       </c>
       <c r="F1187">
         <v>16675</v>
       </c>
       <c r="G1187">
-        <v>4110</v>
+        <v>4186</v>
       </c>
       <c r="H1187">
-        <v>54900</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="1188" spans="1:8">
@@ -31263,25 +31263,25 @@
         <v>1186</v>
       </c>
       <c r="B1188" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C1188">
-        <v>3352</v>
+        <v>3343</v>
       </c>
       <c r="D1188">
-        <v>14672</v>
+        <v>14390</v>
       </c>
       <c r="E1188">
-        <v>1871</v>
+        <v>1870.5</v>
       </c>
       <c r="F1188">
-        <v>16675</v>
+        <v>16630</v>
       </c>
       <c r="G1188">
-        <v>4186</v>
+        <v>4105</v>
       </c>
       <c r="H1188">
-        <v>55000</v>
+        <v>54750</v>
       </c>
     </row>
     <row r="1189" spans="1:8">
@@ -31289,25 +31289,25 @@
         <v>1187</v>
       </c>
       <c r="B1189" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C1189">
-        <v>3343</v>
+        <v>3274</v>
       </c>
       <c r="D1189">
-        <v>14390</v>
+        <v>14238.5</v>
       </c>
       <c r="E1189">
-        <v>1870.5</v>
+        <v>1854</v>
       </c>
       <c r="F1189">
-        <v>16630</v>
+        <v>16270</v>
       </c>
       <c r="G1189">
-        <v>4105</v>
+        <v>4015</v>
       </c>
       <c r="H1189">
-        <v>54750</v>
+        <v>53755</v>
       </c>
     </row>
     <row r="1190" spans="1:8">
@@ -31315,25 +31315,25 @@
         <v>1188</v>
       </c>
       <c r="B1190" s="2">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="C1190">
-        <v>3274</v>
+        <v>3311</v>
       </c>
       <c r="D1190">
-        <v>14238.5</v>
+        <v>14044</v>
       </c>
       <c r="E1190">
-        <v>1854</v>
+        <v>1834</v>
       </c>
       <c r="F1190">
-        <v>16270</v>
+        <v>16205</v>
       </c>
       <c r="G1190">
-        <v>4015</v>
+        <v>3951</v>
       </c>
       <c r="H1190">
-        <v>53755</v>
+        <v>52200</v>
       </c>
     </row>
     <row r="1191" spans="1:8">
@@ -31341,25 +31341,25 @@
         <v>1189</v>
       </c>
       <c r="B1191" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="C1191">
-        <v>3311</v>
+        <v>3260</v>
       </c>
       <c r="D1191">
-        <v>14044</v>
+        <v>14045</v>
       </c>
       <c r="E1191">
-        <v>1834</v>
+        <v>1829</v>
       </c>
       <c r="F1191">
-        <v>16205</v>
+        <v>16135</v>
       </c>
       <c r="G1191">
-        <v>3951</v>
+        <v>3922</v>
       </c>
       <c r="H1191">
-        <v>52200</v>
+        <v>51800</v>
       </c>
     </row>
     <row r="1192" spans="1:8">
@@ -31367,25 +31367,25 @@
         <v>1190</v>
       </c>
       <c r="B1192" s="2">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="C1192">
-        <v>3260</v>
+        <v>3310</v>
       </c>
       <c r="D1192">
-        <v>14045</v>
+        <v>14227</v>
       </c>
       <c r="E1192">
-        <v>1829</v>
+        <v>1848</v>
       </c>
       <c r="F1192">
-        <v>16135</v>
+        <v>16090</v>
       </c>
       <c r="G1192">
-        <v>3922</v>
+        <v>3937</v>
       </c>
       <c r="H1192">
-        <v>51800</v>
+        <v>52310</v>
       </c>
     </row>
     <row r="1193" spans="1:8">
@@ -31393,25 +31393,25 @@
         <v>1191</v>
       </c>
       <c r="B1193" s="2">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="C1193">
-        <v>3310</v>
+        <v>3303.5</v>
       </c>
       <c r="D1193">
-        <v>14227</v>
+        <v>14400.5</v>
       </c>
       <c r="E1193">
-        <v>1848</v>
+        <v>1862</v>
       </c>
       <c r="F1193">
-        <v>16090</v>
+        <v>16170</v>
       </c>
       <c r="G1193">
-        <v>3937</v>
+        <v>3941</v>
       </c>
       <c r="H1193">
-        <v>52310</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="1194" spans="1:8">
@@ -31419,25 +31419,25 @@
         <v>1192</v>
       </c>
       <c r="B1194" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C1194">
-        <v>3303.5</v>
+        <v>3285</v>
       </c>
       <c r="D1194">
-        <v>14400.5</v>
+        <v>14529</v>
       </c>
       <c r="E1194">
-        <v>1862</v>
+        <v>1868</v>
       </c>
       <c r="F1194">
-        <v>16170</v>
+        <v>16055</v>
       </c>
       <c r="G1194">
-        <v>3941</v>
+        <v>4010</v>
       </c>
       <c r="H1194">
-        <v>53000</v>
+        <v>53600</v>
       </c>
     </row>
     <row r="1195" spans="1:8">
@@ -31445,25 +31445,25 @@
         <v>1193</v>
       </c>
       <c r="B1195" s="2">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="C1195">
-        <v>3285</v>
+        <v>3262.5</v>
       </c>
       <c r="D1195">
-        <v>14529</v>
+        <v>14788</v>
       </c>
       <c r="E1195">
-        <v>1868</v>
+        <v>1890</v>
       </c>
       <c r="F1195">
-        <v>16055</v>
+        <v>16125</v>
       </c>
       <c r="G1195">
-        <v>4010</v>
+        <v>4018</v>
       </c>
       <c r="H1195">
-        <v>53600</v>
+        <v>53785</v>
       </c>
     </row>
     <row r="1196" spans="1:8">
@@ -31471,25 +31471,25 @@
         <v>1194</v>
       </c>
       <c r="B1196" s="2">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C1196">
-        <v>3262.5</v>
+        <v>3242</v>
       </c>
       <c r="D1196">
-        <v>14788</v>
+        <v>14797</v>
       </c>
       <c r="E1196">
-        <v>1890</v>
+        <v>1909</v>
       </c>
       <c r="F1196">
-        <v>16125</v>
+        <v>16410</v>
       </c>
       <c r="G1196">
-        <v>4018</v>
+        <v>4006</v>
       </c>
       <c r="H1196">
-        <v>53785</v>
+        <v>53745</v>
       </c>
     </row>
     <row r="1197" spans="1:8">
@@ -31497,25 +31497,25 @@
         <v>1195</v>
       </c>
       <c r="B1197" s="2">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="C1197">
-        <v>3242</v>
+        <v>3240</v>
       </c>
       <c r="D1197">
-        <v>14797</v>
+        <v>14735</v>
       </c>
       <c r="E1197">
-        <v>1909</v>
+        <v>1885.5</v>
       </c>
       <c r="F1197">
-        <v>16410</v>
+        <v>16430</v>
       </c>
       <c r="G1197">
-        <v>4006</v>
+        <v>3949</v>
       </c>
       <c r="H1197">
-        <v>53745</v>
+        <v>54050</v>
       </c>
     </row>
     <row r="1198" spans="1:8">
@@ -31523,25 +31523,25 @@
         <v>1196</v>
       </c>
       <c r="B1198" s="2">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="C1198">
-        <v>3240</v>
+        <v>3228</v>
       </c>
       <c r="D1198">
-        <v>14735</v>
+        <v>14765</v>
       </c>
       <c r="E1198">
-        <v>1885.5</v>
+        <v>1900</v>
       </c>
       <c r="F1198">
-        <v>16430</v>
+        <v>16320</v>
       </c>
       <c r="G1198">
-        <v>3949</v>
+        <v>3981</v>
       </c>
       <c r="H1198">
-        <v>54050</v>
+        <v>53875</v>
       </c>
     </row>
     <row r="1199" spans="1:8">
@@ -31549,25 +31549,25 @@
         <v>1197</v>
       </c>
       <c r="B1199" s="2">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="C1199">
-        <v>3228</v>
+        <v>3254</v>
       </c>
       <c r="D1199">
-        <v>14765</v>
+        <v>14740</v>
       </c>
       <c r="E1199">
-        <v>1900</v>
+        <v>1902.5</v>
       </c>
       <c r="F1199">
-        <v>16320</v>
+        <v>16050</v>
       </c>
       <c r="G1199">
-        <v>3981</v>
+        <v>4060</v>
       </c>
       <c r="H1199">
-        <v>53875</v>
+        <v>54025</v>
       </c>
     </row>
     <row r="1200" spans="1:8">
@@ -31575,25 +31575,25 @@
         <v>1198</v>
       </c>
       <c r="B1200" s="2">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="C1200">
-        <v>3254</v>
+        <v>3248.5</v>
       </c>
       <c r="D1200">
-        <v>14740</v>
+        <v>14544.5</v>
       </c>
       <c r="E1200">
-        <v>1902.5</v>
+        <v>1886</v>
       </c>
       <c r="F1200">
         <v>16050</v>
       </c>
       <c r="G1200">
-        <v>4060</v>
+        <v>3957</v>
       </c>
       <c r="H1200">
-        <v>54025</v>
+        <v>53750</v>
       </c>
     </row>
     <row r="1201" spans="1:8">
@@ -31601,25 +31601,25 @@
         <v>1199</v>
       </c>
       <c r="B1201" s="2">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C1201">
-        <v>3248.5</v>
+        <v>3225.5</v>
       </c>
       <c r="D1201">
-        <v>14544.5</v>
+        <v>14474.5</v>
       </c>
       <c r="E1201">
-        <v>1886</v>
+        <v>1876</v>
       </c>
       <c r="F1201">
-        <v>16050</v>
+        <v>15860</v>
       </c>
       <c r="G1201">
-        <v>3957</v>
+        <v>3977</v>
       </c>
       <c r="H1201">
-        <v>53750</v>
+        <v>53950</v>
       </c>
     </row>
     <row r="1202" spans="1:8">
@@ -31627,50 +31627,24 @@
         <v>1200</v>
       </c>
       <c r="B1202" s="2">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="C1202">
-        <v>3225.5</v>
+        <v>3204</v>
       </c>
       <c r="D1202">
-        <v>14474.5</v>
+        <v>14487</v>
       </c>
       <c r="E1202">
-        <v>1876</v>
+        <v>1856</v>
       </c>
       <c r="F1202">
         <v>15860</v>
       </c>
       <c r="G1202">
-        <v>3977</v>
+        <v>3954</v>
       </c>
       <c r="H1202">
-        <v>53950</v>
-      </c>
-    </row>
-    <row r="1203" spans="1:8">
-      <c r="A1203" s="1">
-        <v>1201</v>
-      </c>
-      <c r="B1203" s="2">
-        <v>46295</v>
-      </c>
-      <c r="C1203">
-        <v>3204</v>
-      </c>
-      <c r="D1203">
-        <v>14487</v>
-      </c>
-      <c r="E1203">
-        <v>1856</v>
-      </c>
-      <c r="F1203">
-        <v>15860</v>
-      </c>
-      <c r="G1203">
-        <v>3954</v>
-      </c>
-      <c r="H1203">
         <v>54075</v>
       </c>
     </row>

--- a/LME/parser/westmetall/data/LME_westmetall_db.xlsx
+++ b/LME/parser/westmetall/data/LME_westmetall_db.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1202"/>
+  <dimension ref="A1:H1200"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28871,25 +28871,25 @@
         <v>1094</v>
       </c>
       <c r="B1096" s="2">
-        <v>46144</v>
+        <v>46147</v>
       </c>
       <c r="C1096">
-        <v>3584</v>
+        <v>3632.5</v>
       </c>
       <c r="D1096">
-        <v>12895</v>
+        <v>12970</v>
       </c>
       <c r="E1096">
-        <v>1945</v>
+        <v>1967</v>
       </c>
       <c r="F1096">
-        <v>19180</v>
+        <v>19295</v>
       </c>
       <c r="G1096">
-        <v>3349</v>
+        <v>3348</v>
       </c>
       <c r="H1096">
-        <v>49200</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="1097" spans="1:8">
@@ -28897,25 +28897,25 @@
         <v>1095</v>
       </c>
       <c r="B1097" s="2">
-        <v>46146</v>
+        <v>46148</v>
       </c>
       <c r="C1097">
-        <v>3584</v>
+        <v>3597</v>
       </c>
       <c r="D1097">
-        <v>12895</v>
+        <v>13351.5</v>
       </c>
       <c r="E1097">
-        <v>1945</v>
+        <v>1987</v>
       </c>
       <c r="F1097">
-        <v>19180</v>
+        <v>19450</v>
       </c>
       <c r="G1097">
-        <v>3349</v>
+        <v>3402</v>
       </c>
       <c r="H1097">
-        <v>49200</v>
+        <v>52465</v>
       </c>
     </row>
     <row r="1098" spans="1:8">
@@ -28923,25 +28923,25 @@
         <v>1096</v>
       </c>
       <c r="B1098" s="2">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="C1098">
-        <v>3632.5</v>
+        <v>3559</v>
       </c>
       <c r="D1098">
-        <v>12970</v>
+        <v>13326</v>
       </c>
       <c r="E1098">
-        <v>1967</v>
+        <v>1980</v>
       </c>
       <c r="F1098">
-        <v>19295</v>
+        <v>18825</v>
       </c>
       <c r="G1098">
-        <v>3348</v>
+        <v>3425</v>
       </c>
       <c r="H1098">
-        <v>49800</v>
+        <v>54550</v>
       </c>
     </row>
     <row r="1099" spans="1:8">
@@ -28949,25 +28949,25 @@
         <v>1097</v>
       </c>
       <c r="B1099" s="2">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="C1099">
-        <v>3597</v>
+        <v>3560.5</v>
       </c>
       <c r="D1099">
-        <v>13351.5</v>
+        <v>13445</v>
       </c>
       <c r="E1099">
-        <v>1987</v>
+        <v>1967</v>
       </c>
       <c r="F1099">
-        <v>19450</v>
+        <v>18890</v>
       </c>
       <c r="G1099">
-        <v>3402</v>
+        <v>3417</v>
       </c>
       <c r="H1099">
-        <v>52465</v>
+        <v>53910</v>
       </c>
     </row>
     <row r="1100" spans="1:8">
@@ -28975,25 +28975,25 @@
         <v>1098</v>
       </c>
       <c r="B1100" s="2">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="C1100">
-        <v>3559</v>
+        <v>3655</v>
       </c>
       <c r="D1100">
-        <v>13326</v>
+        <v>13673</v>
       </c>
       <c r="E1100">
-        <v>1980</v>
+        <v>1977</v>
       </c>
       <c r="F1100">
-        <v>18825</v>
+        <v>18955</v>
       </c>
       <c r="G1100">
-        <v>3425</v>
+        <v>3442</v>
       </c>
       <c r="H1100">
-        <v>54550</v>
+        <v>54975</v>
       </c>
     </row>
     <row r="1101" spans="1:8">
@@ -29001,25 +29001,25 @@
         <v>1099</v>
       </c>
       <c r="B1101" s="2">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="C1101">
-        <v>3560.5</v>
+        <v>3639.5</v>
       </c>
       <c r="D1101">
-        <v>13445</v>
+        <v>13872</v>
       </c>
       <c r="E1101">
-        <v>1967</v>
+        <v>2005</v>
       </c>
       <c r="F1101">
-        <v>18890</v>
+        <v>18725</v>
       </c>
       <c r="G1101">
-        <v>3417</v>
+        <v>3498</v>
       </c>
       <c r="H1101">
-        <v>53910</v>
+        <v>55425</v>
       </c>
     </row>
     <row r="1102" spans="1:8">
@@ -29027,25 +29027,25 @@
         <v>1100</v>
       </c>
       <c r="B1102" s="2">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="C1102">
-        <v>3655</v>
+        <v>3729.5</v>
       </c>
       <c r="D1102">
-        <v>13673</v>
+        <v>14097</v>
       </c>
       <c r="E1102">
-        <v>1977</v>
+        <v>2035</v>
       </c>
       <c r="F1102">
-        <v>18955</v>
+        <v>19020</v>
       </c>
       <c r="G1102">
-        <v>3442</v>
+        <v>3517</v>
       </c>
       <c r="H1102">
-        <v>54975</v>
+        <v>55750</v>
       </c>
     </row>
     <row r="1103" spans="1:8">
@@ -29053,25 +29053,25 @@
         <v>1101</v>
       </c>
       <c r="B1103" s="2">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="C1103">
-        <v>3639.5</v>
+        <v>3768</v>
       </c>
       <c r="D1103">
-        <v>13872</v>
+        <v>13986</v>
       </c>
       <c r="E1103">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="F1103">
-        <v>18725</v>
+        <v>18915</v>
       </c>
       <c r="G1103">
-        <v>3498</v>
+        <v>3596</v>
       </c>
       <c r="H1103">
-        <v>55425</v>
+        <v>55800</v>
       </c>
     </row>
     <row r="1104" spans="1:8">
@@ -29079,25 +29079,25 @@
         <v>1102</v>
       </c>
       <c r="B1104" s="2">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="C1104">
-        <v>3729.5</v>
+        <v>3635</v>
       </c>
       <c r="D1104">
-        <v>14097</v>
+        <v>13553.5</v>
       </c>
       <c r="E1104">
-        <v>2035</v>
+        <v>1995</v>
       </c>
       <c r="F1104">
-        <v>19020</v>
+        <v>18390</v>
       </c>
       <c r="G1104">
-        <v>3517</v>
+        <v>3527</v>
       </c>
       <c r="H1104">
-        <v>55750</v>
+        <v>52900</v>
       </c>
     </row>
     <row r="1105" spans="1:8">
@@ -29105,25 +29105,25 @@
         <v>1103</v>
       </c>
       <c r="B1105" s="2">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="C1105">
-        <v>3768</v>
+        <v>3637</v>
       </c>
       <c r="D1105">
-        <v>13986</v>
+        <v>13428</v>
       </c>
       <c r="E1105">
-        <v>2007</v>
+        <v>1995</v>
       </c>
       <c r="F1105">
-        <v>18915</v>
+        <v>18235</v>
       </c>
       <c r="G1105">
-        <v>3596</v>
+        <v>3529</v>
       </c>
       <c r="H1105">
-        <v>55800</v>
+        <v>52400</v>
       </c>
     </row>
     <row r="1106" spans="1:8">
@@ -29131,25 +29131,25 @@
         <v>1104</v>
       </c>
       <c r="B1106" s="2">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="C1106">
-        <v>3635</v>
+        <v>3665</v>
       </c>
       <c r="D1106">
-        <v>13553.5</v>
+        <v>13410</v>
       </c>
       <c r="E1106">
-        <v>1995</v>
+        <v>1967.5</v>
       </c>
       <c r="F1106">
-        <v>18390</v>
+        <v>18800</v>
       </c>
       <c r="G1106">
-        <v>3527</v>
+        <v>3517</v>
       </c>
       <c r="H1106">
-        <v>52900</v>
+        <v>52800</v>
       </c>
     </row>
     <row r="1107" spans="1:8">
@@ -29157,25 +29157,25 @@
         <v>1105</v>
       </c>
       <c r="B1107" s="2">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="C1107">
-        <v>3637</v>
+        <v>3644</v>
       </c>
       <c r="D1107">
-        <v>13428</v>
+        <v>13418</v>
       </c>
       <c r="E1107">
-        <v>1995</v>
+        <v>1967</v>
       </c>
       <c r="F1107">
-        <v>18235</v>
+        <v>18600</v>
       </c>
       <c r="G1107">
-        <v>3529</v>
+        <v>3519</v>
       </c>
       <c r="H1107">
-        <v>52400</v>
+        <v>54200</v>
       </c>
     </row>
     <row r="1108" spans="1:8">
@@ -29183,22 +29183,22 @@
         <v>1106</v>
       </c>
       <c r="B1108" s="2">
-        <v>46161</v>
+        <v>46163</v>
       </c>
       <c r="C1108">
-        <v>3665</v>
+        <v>3720</v>
       </c>
       <c r="D1108">
-        <v>13410</v>
+        <v>13427</v>
       </c>
       <c r="E1108">
-        <v>1967.5</v>
+        <v>1997</v>
       </c>
       <c r="F1108">
-        <v>18800</v>
+        <v>18540</v>
       </c>
       <c r="G1108">
-        <v>3517</v>
+        <v>3527.5</v>
       </c>
       <c r="H1108">
         <v>52800</v>
@@ -29209,25 +29209,25 @@
         <v>1107</v>
       </c>
       <c r="B1109" s="2">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="C1109">
-        <v>3644</v>
+        <v>3706</v>
       </c>
       <c r="D1109">
-        <v>13418</v>
+        <v>13545</v>
       </c>
       <c r="E1109">
-        <v>1967</v>
+        <v>2006</v>
       </c>
       <c r="F1109">
-        <v>18600</v>
+        <v>18550</v>
       </c>
       <c r="G1109">
-        <v>3519</v>
+        <v>3544.5</v>
       </c>
       <c r="H1109">
-        <v>54200</v>
+        <v>53900</v>
       </c>
     </row>
     <row r="1110" spans="1:8">
@@ -29235,25 +29235,25 @@
         <v>1108</v>
       </c>
       <c r="B1110" s="2">
-        <v>46163</v>
+        <v>46168</v>
       </c>
       <c r="C1110">
-        <v>3720</v>
+        <v>3759</v>
       </c>
       <c r="D1110">
-        <v>13427</v>
+        <v>13570</v>
       </c>
       <c r="E1110">
-        <v>1997</v>
+        <v>2020</v>
       </c>
       <c r="F1110">
-        <v>18540</v>
+        <v>18560</v>
       </c>
       <c r="G1110">
-        <v>3527.5</v>
+        <v>3567</v>
       </c>
       <c r="H1110">
-        <v>52800</v>
+        <v>54575</v>
       </c>
     </row>
     <row r="1111" spans="1:8">
@@ -29261,25 +29261,25 @@
         <v>1109</v>
       </c>
       <c r="B1111" s="2">
-        <v>46164</v>
+        <v>46169</v>
       </c>
       <c r="C1111">
-        <v>3706</v>
+        <v>3738</v>
       </c>
       <c r="D1111">
-        <v>13545</v>
+        <v>13540.5</v>
       </c>
       <c r="E1111">
-        <v>2006</v>
+        <v>2011</v>
       </c>
       <c r="F1111">
-        <v>18550</v>
+        <v>18755</v>
       </c>
       <c r="G1111">
-        <v>3544.5</v>
+        <v>3516</v>
       </c>
       <c r="H1111">
-        <v>53900</v>
+        <v>54700</v>
       </c>
     </row>
     <row r="1112" spans="1:8">
@@ -29287,25 +29287,25 @@
         <v>1110</v>
       </c>
       <c r="B1112" s="2">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="C1112">
-        <v>3759</v>
+        <v>3735</v>
       </c>
       <c r="D1112">
-        <v>13570</v>
+        <v>13513</v>
       </c>
       <c r="E1112">
-        <v>2020</v>
+        <v>1985</v>
       </c>
       <c r="F1112">
-        <v>18560</v>
+        <v>18735</v>
       </c>
       <c r="G1112">
-        <v>3567</v>
+        <v>3486</v>
       </c>
       <c r="H1112">
-        <v>54575</v>
+        <v>54900</v>
       </c>
     </row>
     <row r="1113" spans="1:8">
@@ -29313,25 +29313,25 @@
         <v>1111</v>
       </c>
       <c r="B1113" s="2">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="C1113">
-        <v>3738</v>
+        <v>3769.5</v>
       </c>
       <c r="D1113">
-        <v>13540.5</v>
+        <v>13615</v>
       </c>
       <c r="E1113">
-        <v>2011</v>
+        <v>2016</v>
       </c>
       <c r="F1113">
-        <v>18755</v>
+        <v>18875</v>
       </c>
       <c r="G1113">
-        <v>3516</v>
+        <v>3549</v>
       </c>
       <c r="H1113">
-        <v>54700</v>
+        <v>55010</v>
       </c>
     </row>
     <row r="1114" spans="1:8">
@@ -29339,25 +29339,25 @@
         <v>1112</v>
       </c>
       <c r="B1114" s="2">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="C1114">
-        <v>3735</v>
+        <v>3795.5</v>
       </c>
       <c r="D1114">
-        <v>13513</v>
+        <v>13819</v>
       </c>
       <c r="E1114">
-        <v>1985</v>
+        <v>2008</v>
       </c>
       <c r="F1114">
-        <v>18735</v>
+        <v>19050</v>
       </c>
       <c r="G1114">
-        <v>3486</v>
+        <v>3555</v>
       </c>
       <c r="H1114">
-        <v>54900</v>
+        <v>56400</v>
       </c>
     </row>
     <row r="1115" spans="1:8">
@@ -29365,25 +29365,25 @@
         <v>1113</v>
       </c>
       <c r="B1115" s="2">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="C1115">
-        <v>3769.5</v>
+        <v>3855</v>
       </c>
       <c r="D1115">
-        <v>13615</v>
+        <v>13966</v>
       </c>
       <c r="E1115">
-        <v>2016</v>
+        <v>2025</v>
       </c>
       <c r="F1115">
-        <v>18875</v>
+        <v>19170</v>
       </c>
       <c r="G1115">
-        <v>3549</v>
+        <v>3612</v>
       </c>
       <c r="H1115">
-        <v>55010</v>
+        <v>57525</v>
       </c>
     </row>
     <row r="1116" spans="1:8">
@@ -29391,25 +29391,25 @@
         <v>1114</v>
       </c>
       <c r="B1116" s="2">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="C1116">
-        <v>3795.5</v>
+        <v>3797</v>
       </c>
       <c r="D1116">
-        <v>13819</v>
+        <v>13920.5</v>
       </c>
       <c r="E1116">
-        <v>2008</v>
+        <v>2035</v>
       </c>
       <c r="F1116">
-        <v>19050</v>
+        <v>18810</v>
       </c>
       <c r="G1116">
-        <v>3555</v>
+        <v>3624.5</v>
       </c>
       <c r="H1116">
-        <v>56400</v>
+        <v>57110</v>
       </c>
     </row>
     <row r="1117" spans="1:8">
@@ -29417,25 +29417,25 @@
         <v>1115</v>
       </c>
       <c r="B1117" s="2">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="C1117">
-        <v>3855</v>
+        <v>3739</v>
       </c>
       <c r="D1117">
-        <v>13966</v>
+        <v>13872</v>
       </c>
       <c r="E1117">
-        <v>2025</v>
+        <v>2015</v>
       </c>
       <c r="F1117">
-        <v>19170</v>
+        <v>18375</v>
       </c>
       <c r="G1117">
-        <v>3612</v>
+        <v>3564</v>
       </c>
       <c r="H1117">
-        <v>57525</v>
+        <v>55600</v>
       </c>
     </row>
     <row r="1118" spans="1:8">
@@ -29443,25 +29443,25 @@
         <v>1116</v>
       </c>
       <c r="B1118" s="2">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="C1118">
-        <v>3797</v>
+        <v>3736</v>
       </c>
       <c r="D1118">
-        <v>13920.5</v>
+        <v>13731</v>
       </c>
       <c r="E1118">
-        <v>2035</v>
+        <v>2003</v>
       </c>
       <c r="F1118">
-        <v>18810</v>
+        <v>18545</v>
       </c>
       <c r="G1118">
-        <v>3624.5</v>
+        <v>3575</v>
       </c>
       <c r="H1118">
-        <v>57110</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="1119" spans="1:8">
@@ -29469,25 +29469,25 @@
         <v>1117</v>
       </c>
       <c r="B1119" s="2">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="C1119">
-        <v>3739</v>
+        <v>3669.5</v>
       </c>
       <c r="D1119">
-        <v>13872</v>
+        <v>13661</v>
       </c>
       <c r="E1119">
-        <v>2015</v>
+        <v>1990</v>
       </c>
       <c r="F1119">
-        <v>18375</v>
+        <v>18340</v>
       </c>
       <c r="G1119">
-        <v>3564</v>
+        <v>3519</v>
       </c>
       <c r="H1119">
-        <v>55600</v>
+        <v>51850</v>
       </c>
     </row>
     <row r="1120" spans="1:8">
@@ -29495,25 +29495,25 @@
         <v>1118</v>
       </c>
       <c r="B1120" s="2">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="C1120">
-        <v>3736</v>
+        <v>3608</v>
       </c>
       <c r="D1120">
-        <v>13731</v>
+        <v>13716</v>
       </c>
       <c r="E1120">
-        <v>2003</v>
+        <v>1983</v>
       </c>
       <c r="F1120">
-        <v>18545</v>
+        <v>17930</v>
       </c>
       <c r="G1120">
-        <v>3575</v>
+        <v>3576</v>
       </c>
       <c r="H1120">
-        <v>54000</v>
+        <v>53060</v>
       </c>
     </row>
     <row r="1121" spans="1:8">
@@ -29521,25 +29521,25 @@
         <v>1119</v>
       </c>
       <c r="B1121" s="2">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="C1121">
-        <v>3669.5</v>
+        <v>3489</v>
       </c>
       <c r="D1121">
-        <v>13661</v>
+        <v>13370</v>
       </c>
       <c r="E1121">
-        <v>1990</v>
+        <v>1974.5</v>
       </c>
       <c r="F1121">
-        <v>18340</v>
+        <v>17380</v>
       </c>
       <c r="G1121">
-        <v>3519</v>
+        <v>3486</v>
       </c>
       <c r="H1121">
-        <v>51850</v>
+        <v>51750</v>
       </c>
     </row>
     <row r="1122" spans="1:8">
@@ -29547,25 +29547,25 @@
         <v>1120</v>
       </c>
       <c r="B1122" s="2">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="C1122">
-        <v>3608</v>
+        <v>3498.5</v>
       </c>
       <c r="D1122">
-        <v>13716</v>
+        <v>13420</v>
       </c>
       <c r="E1122">
-        <v>1983</v>
+        <v>1967</v>
       </c>
       <c r="F1122">
-        <v>17930</v>
+        <v>17440</v>
       </c>
       <c r="G1122">
-        <v>3576</v>
+        <v>3468</v>
       </c>
       <c r="H1122">
-        <v>53060</v>
+        <v>52395</v>
       </c>
     </row>
     <row r="1123" spans="1:8">
@@ -29573,25 +29573,25 @@
         <v>1121</v>
       </c>
       <c r="B1123" s="2">
-        <v>46183</v>
+        <v>46185</v>
       </c>
       <c r="C1123">
-        <v>3489</v>
+        <v>3536</v>
       </c>
       <c r="D1123">
-        <v>13370</v>
+        <v>13603</v>
       </c>
       <c r="E1123">
-        <v>1974.5</v>
+        <v>1957</v>
       </c>
       <c r="F1123">
-        <v>17380</v>
+        <v>17630</v>
       </c>
       <c r="G1123">
-        <v>3486</v>
+        <v>3557</v>
       </c>
       <c r="H1123">
-        <v>51750</v>
+        <v>53350</v>
       </c>
     </row>
     <row r="1124" spans="1:8">
@@ -29599,25 +29599,25 @@
         <v>1122</v>
       </c>
       <c r="B1124" s="2">
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="C1124">
-        <v>3498.5</v>
+        <v>3419.5</v>
       </c>
       <c r="D1124">
-        <v>13420</v>
+        <v>13714</v>
       </c>
       <c r="E1124">
-        <v>1967</v>
+        <v>1964</v>
       </c>
       <c r="F1124">
-        <v>17440</v>
+        <v>17810</v>
       </c>
       <c r="G1124">
-        <v>3468</v>
+        <v>3562</v>
       </c>
       <c r="H1124">
-        <v>52395</v>
+        <v>54650</v>
       </c>
     </row>
     <row r="1125" spans="1:8">
@@ -29625,25 +29625,25 @@
         <v>1123</v>
       </c>
       <c r="B1125" s="2">
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="C1125">
-        <v>3536</v>
+        <v>3359</v>
       </c>
       <c r="D1125">
-        <v>13603</v>
+        <v>13682</v>
       </c>
       <c r="E1125">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="F1125">
         <v>17630</v>
       </c>
       <c r="G1125">
-        <v>3557</v>
+        <v>3550</v>
       </c>
       <c r="H1125">
-        <v>53350</v>
+        <v>55150</v>
       </c>
     </row>
     <row r="1126" spans="1:8">
@@ -29651,25 +29651,25 @@
         <v>1124</v>
       </c>
       <c r="B1126" s="2">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="C1126">
-        <v>3419.5</v>
+        <v>3405.5</v>
       </c>
       <c r="D1126">
-        <v>13714</v>
+        <v>13736</v>
       </c>
       <c r="E1126">
-        <v>1964</v>
+        <v>1945</v>
       </c>
       <c r="F1126">
-        <v>17810</v>
+        <v>17820</v>
       </c>
       <c r="G1126">
-        <v>3562</v>
+        <v>3592</v>
       </c>
       <c r="H1126">
-        <v>54650</v>
+        <v>55400</v>
       </c>
     </row>
     <row r="1127" spans="1:8">
@@ -29677,25 +29677,25 @@
         <v>1125</v>
       </c>
       <c r="B1127" s="2">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="C1127">
-        <v>3359</v>
+        <v>3402</v>
       </c>
       <c r="D1127">
-        <v>13682</v>
+        <v>13612</v>
       </c>
       <c r="E1127">
-        <v>1956</v>
+        <v>1945</v>
       </c>
       <c r="F1127">
-        <v>17630</v>
+        <v>17770</v>
       </c>
       <c r="G1127">
-        <v>3550</v>
+        <v>3565</v>
       </c>
       <c r="H1127">
-        <v>55150</v>
+        <v>53455</v>
       </c>
     </row>
     <row r="1128" spans="1:8">
@@ -29703,25 +29703,25 @@
         <v>1126</v>
       </c>
       <c r="B1128" s="2">
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="C1128">
-        <v>3405.5</v>
+        <v>3400</v>
       </c>
       <c r="D1128">
-        <v>13736</v>
+        <v>13530.5</v>
       </c>
       <c r="E1128">
-        <v>1945</v>
+        <v>1935</v>
       </c>
       <c r="F1128">
-        <v>17820</v>
+        <v>17590</v>
       </c>
       <c r="G1128">
-        <v>3592</v>
+        <v>3584.5</v>
       </c>
       <c r="H1128">
-        <v>55400</v>
+        <v>53200</v>
       </c>
     </row>
     <row r="1129" spans="1:8">
@@ -29729,25 +29729,25 @@
         <v>1127</v>
       </c>
       <c r="B1129" s="2">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="C1129">
-        <v>3402</v>
+        <v>3405</v>
       </c>
       <c r="D1129">
-        <v>13612</v>
+        <v>13642</v>
       </c>
       <c r="E1129">
-        <v>1945</v>
+        <v>1928.5</v>
       </c>
       <c r="F1129">
-        <v>17770</v>
+        <v>17640</v>
       </c>
       <c r="G1129">
-        <v>3565</v>
+        <v>3612.5</v>
       </c>
       <c r="H1129">
-        <v>53455</v>
+        <v>54995</v>
       </c>
     </row>
     <row r="1130" spans="1:8">
@@ -29755,25 +29755,25 @@
         <v>1128</v>
       </c>
       <c r="B1130" s="2">
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="C1130">
-        <v>3400</v>
+        <v>3263.5</v>
       </c>
       <c r="D1130">
-        <v>13530.5</v>
+        <v>13334</v>
       </c>
       <c r="E1130">
-        <v>1935</v>
+        <v>1910</v>
       </c>
       <c r="F1130">
-        <v>17590</v>
+        <v>17105</v>
       </c>
       <c r="G1130">
-        <v>3584.5</v>
+        <v>3503</v>
       </c>
       <c r="H1130">
-        <v>53200</v>
+        <v>51900</v>
       </c>
     </row>
     <row r="1131" spans="1:8">
@@ -29781,25 +29781,25 @@
         <v>1129</v>
       </c>
       <c r="B1131" s="2">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="C1131">
-        <v>3405</v>
+        <v>3150</v>
       </c>
       <c r="D1131">
-        <v>13642</v>
+        <v>13181.5</v>
       </c>
       <c r="E1131">
-        <v>1928.5</v>
+        <v>1896</v>
       </c>
       <c r="F1131">
-        <v>17640</v>
+        <v>16610</v>
       </c>
       <c r="G1131">
-        <v>3612.5</v>
+        <v>3437</v>
       </c>
       <c r="H1131">
-        <v>54995</v>
+        <v>49550</v>
       </c>
     </row>
     <row r="1132" spans="1:8">
@@ -29807,25 +29807,25 @@
         <v>1130</v>
       </c>
       <c r="B1132" s="2">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="C1132">
-        <v>3263.5</v>
+        <v>3132</v>
       </c>
       <c r="D1132">
-        <v>13334</v>
+        <v>13194</v>
       </c>
       <c r="E1132">
-        <v>1910</v>
+        <v>1894</v>
       </c>
       <c r="F1132">
-        <v>17105</v>
+        <v>16660</v>
       </c>
       <c r="G1132">
-        <v>3503</v>
+        <v>3432</v>
       </c>
       <c r="H1132">
-        <v>51900</v>
+        <v>50100</v>
       </c>
     </row>
     <row r="1133" spans="1:8">
@@ -29833,25 +29833,25 @@
         <v>1131</v>
       </c>
       <c r="B1133" s="2">
-        <v>46197</v>
+        <v>46199</v>
       </c>
       <c r="C1133">
-        <v>3150</v>
+        <v>3164</v>
       </c>
       <c r="D1133">
-        <v>13181.5</v>
+        <v>13287</v>
       </c>
       <c r="E1133">
-        <v>1896</v>
+        <v>1880</v>
       </c>
       <c r="F1133">
-        <v>16610</v>
+        <v>16570</v>
       </c>
       <c r="G1133">
-        <v>3437</v>
+        <v>3460</v>
       </c>
       <c r="H1133">
-        <v>49550</v>
+        <v>50325</v>
       </c>
     </row>
     <row r="1134" spans="1:8">
@@ -29859,25 +29859,25 @@
         <v>1132</v>
       </c>
       <c r="B1134" s="2">
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="C1134">
-        <v>3132</v>
+        <v>3160.5</v>
       </c>
       <c r="D1134">
-        <v>13194</v>
+        <v>13302.5</v>
       </c>
       <c r="E1134">
-        <v>1894</v>
+        <v>1871.5</v>
       </c>
       <c r="F1134">
-        <v>16660</v>
+        <v>16455</v>
       </c>
       <c r="G1134">
-        <v>3432</v>
+        <v>3491</v>
       </c>
       <c r="H1134">
-        <v>50100</v>
+        <v>51000</v>
       </c>
     </row>
     <row r="1135" spans="1:8">
@@ -29885,25 +29885,25 @@
         <v>1133</v>
       </c>
       <c r="B1135" s="2">
-        <v>46199</v>
+        <v>46203</v>
       </c>
       <c r="C1135">
-        <v>3164</v>
+        <v>3105.5</v>
       </c>
       <c r="D1135">
-        <v>13287</v>
+        <v>13341</v>
       </c>
       <c r="E1135">
-        <v>1880</v>
+        <v>1845</v>
       </c>
       <c r="F1135">
-        <v>16570</v>
+        <v>16275</v>
       </c>
       <c r="G1135">
-        <v>3460</v>
+        <v>3565.5</v>
       </c>
       <c r="H1135">
-        <v>50325</v>
+        <v>51100</v>
       </c>
     </row>
     <row r="1136" spans="1:8">
@@ -29911,25 +29911,25 @@
         <v>1134</v>
       </c>
       <c r="B1136" s="2">
-        <v>46202</v>
+        <v>46204</v>
       </c>
       <c r="C1136">
-        <v>3160.5</v>
+        <v>3075</v>
       </c>
       <c r="D1136">
-        <v>13302.5</v>
+        <v>13170</v>
       </c>
       <c r="E1136">
-        <v>1871.5</v>
+        <v>1840</v>
       </c>
       <c r="F1136">
-        <v>16455</v>
+        <v>16175</v>
       </c>
       <c r="G1136">
-        <v>3491</v>
+        <v>3529</v>
       </c>
       <c r="H1136">
-        <v>51000</v>
+        <v>51150</v>
       </c>
     </row>
     <row r="1137" spans="1:8">
@@ -29937,25 +29937,25 @@
         <v>1135</v>
       </c>
       <c r="B1137" s="2">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="C1137">
-        <v>3105.5</v>
+        <v>3061.5</v>
       </c>
       <c r="D1137">
-        <v>13341</v>
+        <v>13202</v>
       </c>
       <c r="E1137">
-        <v>1845</v>
+        <v>1828.5</v>
       </c>
       <c r="F1137">
-        <v>16275</v>
+        <v>16070</v>
       </c>
       <c r="G1137">
-        <v>3565.5</v>
+        <v>3475</v>
       </c>
       <c r="H1137">
-        <v>51100</v>
+        <v>51200</v>
       </c>
     </row>
     <row r="1138" spans="1:8">
@@ -29963,25 +29963,25 @@
         <v>1136</v>
       </c>
       <c r="B1138" s="2">
-        <v>46204</v>
+        <v>46206</v>
       </c>
       <c r="C1138">
-        <v>3075</v>
+        <v>3080</v>
       </c>
       <c r="D1138">
-        <v>13170</v>
+        <v>13298.5</v>
       </c>
       <c r="E1138">
-        <v>1840</v>
+        <v>1851</v>
       </c>
       <c r="F1138">
-        <v>16175</v>
+        <v>16115</v>
       </c>
       <c r="G1138">
-        <v>3529</v>
+        <v>3546</v>
       </c>
       <c r="H1138">
-        <v>51150</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="1139" spans="1:8">
@@ -29989,25 +29989,25 @@
         <v>1137</v>
       </c>
       <c r="B1139" s="2">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="C1139">
-        <v>3061.5</v>
+        <v>3105</v>
       </c>
       <c r="D1139">
-        <v>13202</v>
+        <v>13310</v>
       </c>
       <c r="E1139">
-        <v>1828.5</v>
+        <v>1852.5</v>
       </c>
       <c r="F1139">
-        <v>16070</v>
+        <v>16065</v>
       </c>
       <c r="G1139">
-        <v>3475</v>
+        <v>3599</v>
       </c>
       <c r="H1139">
-        <v>51200</v>
+        <v>52525</v>
       </c>
     </row>
     <row r="1140" spans="1:8">
@@ -30015,25 +30015,25 @@
         <v>1138</v>
       </c>
       <c r="B1140" s="2">
-        <v>46206</v>
+        <v>46210</v>
       </c>
       <c r="C1140">
-        <v>3080</v>
+        <v>3119</v>
       </c>
       <c r="D1140">
-        <v>13298.5</v>
+        <v>13309</v>
       </c>
       <c r="E1140">
-        <v>1851</v>
+        <v>1849</v>
       </c>
       <c r="F1140">
-        <v>16115</v>
+        <v>16160</v>
       </c>
       <c r="G1140">
-        <v>3546</v>
+        <v>3560</v>
       </c>
       <c r="H1140">
-        <v>52000</v>
+        <v>52900</v>
       </c>
     </row>
     <row r="1141" spans="1:8">
@@ -30041,25 +30041,25 @@
         <v>1139</v>
       </c>
       <c r="B1141" s="2">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="C1141">
-        <v>3105</v>
+        <v>3141</v>
       </c>
       <c r="D1141">
-        <v>13310</v>
+        <v>13090</v>
       </c>
       <c r="E1141">
-        <v>1852.5</v>
+        <v>1851</v>
       </c>
       <c r="F1141">
-        <v>16065</v>
+        <v>16160</v>
       </c>
       <c r="G1141">
-        <v>3599</v>
+        <v>3529</v>
       </c>
       <c r="H1141">
-        <v>52525</v>
+        <v>52350</v>
       </c>
     </row>
     <row r="1142" spans="1:8">
@@ -30067,25 +30067,25 @@
         <v>1140</v>
       </c>
       <c r="B1142" s="2">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="C1142">
-        <v>3119</v>
+        <v>3164</v>
       </c>
       <c r="D1142">
-        <v>13309</v>
+        <v>13356.5</v>
       </c>
       <c r="E1142">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="F1142">
-        <v>16160</v>
+        <v>16355</v>
       </c>
       <c r="G1142">
-        <v>3560</v>
+        <v>3622</v>
       </c>
       <c r="H1142">
-        <v>52900</v>
+        <v>53450</v>
       </c>
     </row>
     <row r="1143" spans="1:8">
@@ -30093,25 +30093,25 @@
         <v>1141</v>
       </c>
       <c r="B1143" s="2">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="C1143">
-        <v>3141</v>
+        <v>3156</v>
       </c>
       <c r="D1143">
-        <v>13090</v>
+        <v>13408.5</v>
       </c>
       <c r="E1143">
         <v>1851</v>
       </c>
       <c r="F1143">
-        <v>16160</v>
+        <v>16410</v>
       </c>
       <c r="G1143">
-        <v>3529</v>
+        <v>3602</v>
       </c>
       <c r="H1143">
-        <v>52350</v>
+        <v>52575</v>
       </c>
     </row>
     <row r="1144" spans="1:8">
@@ -30119,25 +30119,25 @@
         <v>1142</v>
       </c>
       <c r="B1144" s="2">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="C1144">
-        <v>3164</v>
+        <v>3138.5</v>
       </c>
       <c r="D1144">
-        <v>13356.5</v>
+        <v>13460.5</v>
       </c>
       <c r="E1144">
-        <v>1850</v>
+        <v>1832</v>
       </c>
       <c r="F1144">
-        <v>16355</v>
+        <v>16405</v>
       </c>
       <c r="G1144">
-        <v>3622</v>
+        <v>3571</v>
       </c>
       <c r="H1144">
-        <v>53450</v>
+        <v>52705</v>
       </c>
     </row>
     <row r="1145" spans="1:8">
@@ -30145,25 +30145,25 @@
         <v>1143</v>
       </c>
       <c r="B1145" s="2">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="C1145">
-        <v>3156</v>
+        <v>3171</v>
       </c>
       <c r="D1145">
-        <v>13408.5</v>
+        <v>13541</v>
       </c>
       <c r="E1145">
-        <v>1851</v>
+        <v>1803</v>
       </c>
       <c r="F1145">
-        <v>16410</v>
+        <v>16590</v>
       </c>
       <c r="G1145">
-        <v>3602</v>
+        <v>3589.5</v>
       </c>
       <c r="H1145">
-        <v>52575</v>
+        <v>53900</v>
       </c>
     </row>
     <row r="1146" spans="1:8">
@@ -30171,22 +30171,22 @@
         <v>1144</v>
       </c>
       <c r="B1146" s="2">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="C1146">
-        <v>3138.5</v>
+        <v>3153.5</v>
       </c>
       <c r="D1146">
-        <v>13460.5</v>
+        <v>13537</v>
       </c>
       <c r="E1146">
-        <v>1832</v>
+        <v>1797</v>
       </c>
       <c r="F1146">
-        <v>16405</v>
+        <v>16505</v>
       </c>
       <c r="G1146">
-        <v>3571</v>
+        <v>3553.5</v>
       </c>
       <c r="H1146">
         <v>52705</v>
@@ -30197,25 +30197,25 @@
         <v>1145</v>
       </c>
       <c r="B1147" s="2">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="C1147">
-        <v>3171</v>
+        <v>3170</v>
       </c>
       <c r="D1147">
-        <v>13541</v>
+        <v>13565</v>
       </c>
       <c r="E1147">
-        <v>1803</v>
+        <v>1827.5</v>
       </c>
       <c r="F1147">
-        <v>16590</v>
+        <v>17150</v>
       </c>
       <c r="G1147">
-        <v>3589.5</v>
+        <v>3591</v>
       </c>
       <c r="H1147">
-        <v>53900</v>
+        <v>52860</v>
       </c>
     </row>
     <row r="1148" spans="1:8">
@@ -30223,25 +30223,25 @@
         <v>1146</v>
       </c>
       <c r="B1148" s="2">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="C1148">
-        <v>3153.5</v>
+        <v>3154</v>
       </c>
       <c r="D1148">
-        <v>13537</v>
+        <v>13373.5</v>
       </c>
       <c r="E1148">
-        <v>1797</v>
+        <v>1821</v>
       </c>
       <c r="F1148">
-        <v>16505</v>
+        <v>16725</v>
       </c>
       <c r="G1148">
-        <v>3553.5</v>
+        <v>3549</v>
       </c>
       <c r="H1148">
-        <v>52705</v>
+        <v>52045</v>
       </c>
     </row>
     <row r="1149" spans="1:8">
@@ -30249,25 +30249,25 @@
         <v>1147</v>
       </c>
       <c r="B1149" s="2">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="C1149">
-        <v>3170</v>
+        <v>3156</v>
       </c>
       <c r="D1149">
-        <v>13565</v>
+        <v>13629</v>
       </c>
       <c r="E1149">
-        <v>1827.5</v>
+        <v>1830</v>
       </c>
       <c r="F1149">
-        <v>17150</v>
+        <v>16850</v>
       </c>
       <c r="G1149">
-        <v>3591</v>
+        <v>3575</v>
       </c>
       <c r="H1149">
-        <v>52860</v>
+        <v>53300</v>
       </c>
     </row>
     <row r="1150" spans="1:8">
@@ -30275,25 +30275,25 @@
         <v>1148</v>
       </c>
       <c r="B1150" s="2">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="C1150">
-        <v>3154</v>
+        <v>3183.5</v>
       </c>
       <c r="D1150">
-        <v>13373.5</v>
+        <v>13856</v>
       </c>
       <c r="E1150">
-        <v>1821</v>
+        <v>1842</v>
       </c>
       <c r="F1150">
-        <v>16725</v>
+        <v>16970</v>
       </c>
       <c r="G1150">
-        <v>3549</v>
+        <v>3591</v>
       </c>
       <c r="H1150">
-        <v>52045</v>
+        <v>54100</v>
       </c>
     </row>
     <row r="1151" spans="1:8">
@@ -30301,25 +30301,25 @@
         <v>1149</v>
       </c>
       <c r="B1151" s="2">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="C1151">
-        <v>3156</v>
+        <v>3205</v>
       </c>
       <c r="D1151">
-        <v>13629</v>
+        <v>13895</v>
       </c>
       <c r="E1151">
-        <v>1830</v>
+        <v>1841.5</v>
       </c>
       <c r="F1151">
-        <v>16850</v>
+        <v>16940</v>
       </c>
       <c r="G1151">
-        <v>3575</v>
+        <v>3614</v>
       </c>
       <c r="H1151">
-        <v>53300</v>
+        <v>53900</v>
       </c>
     </row>
     <row r="1152" spans="1:8">
@@ -30327,25 +30327,25 @@
         <v>1150</v>
       </c>
       <c r="B1152" s="2">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="C1152">
-        <v>3183.5</v>
+        <v>3194</v>
       </c>
       <c r="D1152">
-        <v>13856</v>
+        <v>13745</v>
       </c>
       <c r="E1152">
-        <v>1842</v>
+        <v>1875</v>
       </c>
       <c r="F1152">
-        <v>16970</v>
+        <v>17200</v>
       </c>
       <c r="G1152">
-        <v>3591</v>
+        <v>3653</v>
       </c>
       <c r="H1152">
-        <v>54100</v>
+        <v>53800</v>
       </c>
     </row>
     <row r="1153" spans="1:8">
@@ -30353,25 +30353,25 @@
         <v>1151</v>
       </c>
       <c r="B1153" s="2">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="C1153">
-        <v>3205</v>
+        <v>3175</v>
       </c>
       <c r="D1153">
-        <v>13895</v>
+        <v>13617</v>
       </c>
       <c r="E1153">
-        <v>1841.5</v>
+        <v>1865.5</v>
       </c>
       <c r="F1153">
-        <v>16940</v>
+        <v>17205</v>
       </c>
       <c r="G1153">
-        <v>3614</v>
+        <v>3633</v>
       </c>
       <c r="H1153">
-        <v>53900</v>
+        <v>53250</v>
       </c>
     </row>
     <row r="1154" spans="1:8">
@@ -30379,25 +30379,25 @@
         <v>1152</v>
       </c>
       <c r="B1154" s="2">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="C1154">
-        <v>3194</v>
+        <v>3192</v>
       </c>
       <c r="D1154">
-        <v>13745</v>
+        <v>13810</v>
       </c>
       <c r="E1154">
-        <v>1875</v>
+        <v>1859</v>
       </c>
       <c r="F1154">
-        <v>17200</v>
+        <v>17165</v>
       </c>
       <c r="G1154">
-        <v>3653</v>
+        <v>3685.5</v>
       </c>
       <c r="H1154">
-        <v>53800</v>
+        <v>54250</v>
       </c>
     </row>
     <row r="1155" spans="1:8">
@@ -30405,25 +30405,25 @@
         <v>1153</v>
       </c>
       <c r="B1155" s="2">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="C1155">
-        <v>3175</v>
+        <v>3159.5</v>
       </c>
       <c r="D1155">
-        <v>13617</v>
+        <v>13643.5</v>
       </c>
       <c r="E1155">
-        <v>1865.5</v>
+        <v>1856</v>
       </c>
       <c r="F1155">
-        <v>17205</v>
+        <v>16860</v>
       </c>
       <c r="G1155">
-        <v>3633</v>
+        <v>3631.5</v>
       </c>
       <c r="H1155">
-        <v>53250</v>
+        <v>53600</v>
       </c>
     </row>
     <row r="1156" spans="1:8">
@@ -30431,25 +30431,25 @@
         <v>1154</v>
       </c>
       <c r="B1156" s="2">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="C1156">
-        <v>3192</v>
+        <v>3207</v>
       </c>
       <c r="D1156">
-        <v>13810</v>
+        <v>13633</v>
       </c>
       <c r="E1156">
-        <v>1859</v>
+        <v>1877</v>
       </c>
       <c r="F1156">
-        <v>17165</v>
+        <v>17000</v>
       </c>
       <c r="G1156">
-        <v>3685.5</v>
+        <v>3639</v>
       </c>
       <c r="H1156">
-        <v>54250</v>
+        <v>53990</v>
       </c>
     </row>
     <row r="1157" spans="1:8">
@@ -30457,25 +30457,25 @@
         <v>1155</v>
       </c>
       <c r="B1157" s="2">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="C1157">
-        <v>3159.5</v>
+        <v>3231</v>
       </c>
       <c r="D1157">
-        <v>13643.5</v>
+        <v>13795</v>
       </c>
       <c r="E1157">
-        <v>1856</v>
+        <v>1863</v>
       </c>
       <c r="F1157">
-        <v>16860</v>
+        <v>16945</v>
       </c>
       <c r="G1157">
-        <v>3631.5</v>
+        <v>3662</v>
       </c>
       <c r="H1157">
-        <v>53600</v>
+        <v>54125</v>
       </c>
     </row>
     <row r="1158" spans="1:8">
@@ -30483,25 +30483,25 @@
         <v>1156</v>
       </c>
       <c r="B1158" s="2">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="C1158">
-        <v>3207</v>
+        <v>3196</v>
       </c>
       <c r="D1158">
-        <v>13633</v>
+        <v>13834</v>
       </c>
       <c r="E1158">
-        <v>1877</v>
+        <v>1851.5</v>
       </c>
       <c r="F1158">
-        <v>17000</v>
+        <v>17100</v>
       </c>
       <c r="G1158">
-        <v>3639</v>
+        <v>3710.5</v>
       </c>
       <c r="H1158">
-        <v>53990</v>
+        <v>54660</v>
       </c>
     </row>
     <row r="1159" spans="1:8">
@@ -30509,25 +30509,25 @@
         <v>1157</v>
       </c>
       <c r="B1159" s="2">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="C1159">
-        <v>3231</v>
+        <v>3260</v>
       </c>
       <c r="D1159">
-        <v>13795</v>
+        <v>13945</v>
       </c>
       <c r="E1159">
-        <v>1863</v>
+        <v>1828</v>
       </c>
       <c r="F1159">
-        <v>16945</v>
+        <v>16785</v>
       </c>
       <c r="G1159">
-        <v>3662</v>
+        <v>3751</v>
       </c>
       <c r="H1159">
-        <v>54125</v>
+        <v>55200</v>
       </c>
     </row>
     <row r="1160" spans="1:8">
@@ -30535,25 +30535,25 @@
         <v>1158</v>
       </c>
       <c r="B1160" s="2">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="C1160">
-        <v>3196</v>
+        <v>3271</v>
       </c>
       <c r="D1160">
-        <v>13834</v>
+        <v>14195</v>
       </c>
       <c r="E1160">
-        <v>1851.5</v>
+        <v>1847</v>
       </c>
       <c r="F1160">
-        <v>17100</v>
+        <v>17125</v>
       </c>
       <c r="G1160">
-        <v>3710.5</v>
+        <v>3730</v>
       </c>
       <c r="H1160">
-        <v>54660</v>
+        <v>55700</v>
       </c>
     </row>
     <row r="1161" spans="1:8">
@@ -30561,25 +30561,25 @@
         <v>1159</v>
       </c>
       <c r="B1161" s="2">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="C1161">
-        <v>3260</v>
+        <v>3229</v>
       </c>
       <c r="D1161">
-        <v>13945</v>
+        <v>14167.5</v>
       </c>
       <c r="E1161">
-        <v>1828</v>
+        <v>1845</v>
       </c>
       <c r="F1161">
-        <v>16785</v>
+        <v>16915</v>
       </c>
       <c r="G1161">
-        <v>3751</v>
+        <v>3737</v>
       </c>
       <c r="H1161">
-        <v>55200</v>
+        <v>56225</v>
       </c>
     </row>
     <row r="1162" spans="1:8">
@@ -30587,25 +30587,25 @@
         <v>1160</v>
       </c>
       <c r="B1162" s="2">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="C1162">
-        <v>3271</v>
+        <v>3261</v>
       </c>
       <c r="D1162">
-        <v>14195</v>
+        <v>14455</v>
       </c>
       <c r="E1162">
-        <v>1847</v>
+        <v>1851</v>
       </c>
       <c r="F1162">
-        <v>17125</v>
+        <v>16595</v>
       </c>
       <c r="G1162">
-        <v>3730</v>
+        <v>3857</v>
       </c>
       <c r="H1162">
-        <v>55700</v>
+        <v>56500</v>
       </c>
     </row>
     <row r="1163" spans="1:8">
@@ -30613,25 +30613,25 @@
         <v>1161</v>
       </c>
       <c r="B1163" s="2">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="C1163">
-        <v>3229</v>
+        <v>3279.5</v>
       </c>
       <c r="D1163">
-        <v>14167.5</v>
+        <v>14240</v>
       </c>
       <c r="E1163">
-        <v>1845</v>
+        <v>1840.5</v>
       </c>
       <c r="F1163">
-        <v>16915</v>
+        <v>16745</v>
       </c>
       <c r="G1163">
-        <v>3737</v>
+        <v>3785</v>
       </c>
       <c r="H1163">
-        <v>56225</v>
+        <v>56100</v>
       </c>
     </row>
     <row r="1164" spans="1:8">
@@ -30639,25 +30639,25 @@
         <v>1162</v>
       </c>
       <c r="B1164" s="2">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="C1164">
-        <v>3261</v>
+        <v>3327.5</v>
       </c>
       <c r="D1164">
-        <v>14455</v>
+        <v>14290</v>
       </c>
       <c r="E1164">
-        <v>1851</v>
+        <v>1858</v>
       </c>
       <c r="F1164">
-        <v>16595</v>
+        <v>16775</v>
       </c>
       <c r="G1164">
-        <v>3857</v>
+        <v>3786</v>
       </c>
       <c r="H1164">
-        <v>56500</v>
+        <v>55900</v>
       </c>
     </row>
     <row r="1165" spans="1:8">
@@ -30665,25 +30665,25 @@
         <v>1163</v>
       </c>
       <c r="B1165" s="2">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="C1165">
-        <v>3279.5</v>
+        <v>3373</v>
       </c>
       <c r="D1165">
-        <v>14240</v>
+        <v>14424.5</v>
       </c>
       <c r="E1165">
-        <v>1840.5</v>
+        <v>1878</v>
       </c>
       <c r="F1165">
-        <v>16745</v>
+        <v>16640</v>
       </c>
       <c r="G1165">
-        <v>3785</v>
+        <v>3822</v>
       </c>
       <c r="H1165">
-        <v>56100</v>
+        <v>55305</v>
       </c>
     </row>
     <row r="1166" spans="1:8">
@@ -30691,25 +30691,25 @@
         <v>1164</v>
       </c>
       <c r="B1166" s="2">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="C1166">
-        <v>3327.5</v>
+        <v>3307.5</v>
       </c>
       <c r="D1166">
-        <v>14290</v>
+        <v>14376</v>
       </c>
       <c r="E1166">
-        <v>1858</v>
+        <v>1880</v>
       </c>
       <c r="F1166">
-        <v>16775</v>
+        <v>16725</v>
       </c>
       <c r="G1166">
-        <v>3786</v>
+        <v>3852</v>
       </c>
       <c r="H1166">
-        <v>55900</v>
+        <v>56050</v>
       </c>
     </row>
     <row r="1167" spans="1:8">
@@ -30717,25 +30717,25 @@
         <v>1165</v>
       </c>
       <c r="B1167" s="2">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="C1167">
-        <v>3373</v>
+        <v>3279</v>
       </c>
       <c r="D1167">
-        <v>14424.5</v>
+        <v>14285</v>
       </c>
       <c r="E1167">
-        <v>1878</v>
+        <v>1856</v>
       </c>
       <c r="F1167">
-        <v>16640</v>
+        <v>16690</v>
       </c>
       <c r="G1167">
-        <v>3822</v>
+        <v>3806</v>
       </c>
       <c r="H1167">
-        <v>55305</v>
+        <v>56150</v>
       </c>
     </row>
     <row r="1168" spans="1:8">
@@ -30743,25 +30743,25 @@
         <v>1166</v>
       </c>
       <c r="B1168" s="2">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="C1168">
-        <v>3307.5</v>
+        <v>3248</v>
       </c>
       <c r="D1168">
-        <v>14376</v>
+        <v>14545</v>
       </c>
       <c r="E1168">
-        <v>1880</v>
+        <v>1846</v>
       </c>
       <c r="F1168">
-        <v>16725</v>
+        <v>16575</v>
       </c>
       <c r="G1168">
-        <v>3852</v>
+        <v>3875</v>
       </c>
       <c r="H1168">
-        <v>56050</v>
+        <v>56075</v>
       </c>
     </row>
     <row r="1169" spans="1:8">
@@ -30769,25 +30769,25 @@
         <v>1167</v>
       </c>
       <c r="B1169" s="2">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="C1169">
-        <v>3279</v>
+        <v>3272</v>
       </c>
       <c r="D1169">
-        <v>14285</v>
+        <v>14850</v>
       </c>
       <c r="E1169">
-        <v>1856</v>
+        <v>1851.5</v>
       </c>
       <c r="F1169">
-        <v>16690</v>
+        <v>16670</v>
       </c>
       <c r="G1169">
-        <v>3806</v>
+        <v>3855</v>
       </c>
       <c r="H1169">
-        <v>56150</v>
+        <v>56225</v>
       </c>
     </row>
     <row r="1170" spans="1:8">
@@ -30795,25 +30795,25 @@
         <v>1168</v>
       </c>
       <c r="B1170" s="2">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="C1170">
-        <v>3248</v>
+        <v>3219</v>
       </c>
       <c r="D1170">
-        <v>14545</v>
+        <v>14335</v>
       </c>
       <c r="E1170">
-        <v>1846</v>
+        <v>1840.5</v>
       </c>
       <c r="F1170">
-        <v>16575</v>
+        <v>16740</v>
       </c>
       <c r="G1170">
-        <v>3875</v>
+        <v>3795</v>
       </c>
       <c r="H1170">
-        <v>56075</v>
+        <v>55550</v>
       </c>
     </row>
     <row r="1171" spans="1:8">
@@ -30821,25 +30821,25 @@
         <v>1169</v>
       </c>
       <c r="B1171" s="2">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="C1171">
-        <v>3272</v>
+        <v>3191.5</v>
       </c>
       <c r="D1171">
-        <v>14850</v>
+        <v>14180</v>
       </c>
       <c r="E1171">
-        <v>1851.5</v>
+        <v>1827</v>
       </c>
       <c r="F1171">
-        <v>16670</v>
+        <v>16690</v>
       </c>
       <c r="G1171">
-        <v>3855</v>
+        <v>3750</v>
       </c>
       <c r="H1171">
-        <v>56225</v>
+        <v>54375</v>
       </c>
     </row>
     <row r="1172" spans="1:8">
@@ -30847,25 +30847,25 @@
         <v>1170</v>
       </c>
       <c r="B1172" s="2">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="C1172">
-        <v>3219</v>
+        <v>3182</v>
       </c>
       <c r="D1172">
-        <v>14335</v>
+        <v>14170</v>
       </c>
       <c r="E1172">
-        <v>1840.5</v>
+        <v>1848</v>
       </c>
       <c r="F1172">
-        <v>16740</v>
+        <v>16660</v>
       </c>
       <c r="G1172">
-        <v>3795</v>
+        <v>3865.5</v>
       </c>
       <c r="H1172">
-        <v>55550</v>
+        <v>54850</v>
       </c>
     </row>
     <row r="1173" spans="1:8">
@@ -30873,25 +30873,25 @@
         <v>1171</v>
       </c>
       <c r="B1173" s="2">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="C1173">
-        <v>3191.5</v>
+        <v>3227</v>
       </c>
       <c r="D1173">
-        <v>14180</v>
+        <v>14291</v>
       </c>
       <c r="E1173">
-        <v>1827</v>
+        <v>1857</v>
       </c>
       <c r="F1173">
-        <v>16690</v>
+        <v>16860</v>
       </c>
       <c r="G1173">
-        <v>3750</v>
+        <v>3980</v>
       </c>
       <c r="H1173">
-        <v>54375</v>
+        <v>55900</v>
       </c>
     </row>
     <row r="1174" spans="1:8">
@@ -30899,25 +30899,25 @@
         <v>1172</v>
       </c>
       <c r="B1174" s="2">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="C1174">
-        <v>3182</v>
+        <v>3215.5</v>
       </c>
       <c r="D1174">
-        <v>14170</v>
+        <v>14344</v>
       </c>
       <c r="E1174">
-        <v>1848</v>
+        <v>1862.5</v>
       </c>
       <c r="F1174">
-        <v>16660</v>
+        <v>16940</v>
       </c>
       <c r="G1174">
-        <v>3865.5</v>
+        <v>3985</v>
       </c>
       <c r="H1174">
-        <v>54850</v>
+        <v>55900</v>
       </c>
     </row>
     <row r="1175" spans="1:8">
@@ -30925,25 +30925,25 @@
         <v>1173</v>
       </c>
       <c r="B1175" s="2">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="C1175">
-        <v>3227</v>
+        <v>3188</v>
       </c>
       <c r="D1175">
-        <v>14291</v>
+        <v>14425</v>
       </c>
       <c r="E1175">
-        <v>1857</v>
+        <v>1867</v>
       </c>
       <c r="F1175">
-        <v>16860</v>
+        <v>16780</v>
       </c>
       <c r="G1175">
-        <v>3980</v>
+        <v>3987</v>
       </c>
       <c r="H1175">
-        <v>55900</v>
+        <v>55700</v>
       </c>
     </row>
     <row r="1176" spans="1:8">
@@ -30951,25 +30951,25 @@
         <v>1174</v>
       </c>
       <c r="B1176" s="2">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="C1176">
-        <v>3215.5</v>
+        <v>3227.5</v>
       </c>
       <c r="D1176">
-        <v>14344</v>
+        <v>14525</v>
       </c>
       <c r="E1176">
-        <v>1862.5</v>
+        <v>1866</v>
       </c>
       <c r="F1176">
-        <v>16940</v>
+        <v>16895</v>
       </c>
       <c r="G1176">
-        <v>3985</v>
+        <v>4107</v>
       </c>
       <c r="H1176">
-        <v>55900</v>
+        <v>55300</v>
       </c>
     </row>
     <row r="1177" spans="1:8">
@@ -30977,25 +30977,25 @@
         <v>1175</v>
       </c>
       <c r="B1177" s="2">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="C1177">
-        <v>3188</v>
+        <v>3212.5</v>
       </c>
       <c r="D1177">
-        <v>14425</v>
+        <v>14490</v>
       </c>
       <c r="E1177">
-        <v>1867</v>
+        <v>1872</v>
       </c>
       <c r="F1177">
-        <v>16780</v>
+        <v>16660</v>
       </c>
       <c r="G1177">
-        <v>3987</v>
+        <v>4107</v>
       </c>
       <c r="H1177">
-        <v>55700</v>
+        <v>54950</v>
       </c>
     </row>
     <row r="1178" spans="1:8">
@@ -31003,25 +31003,25 @@
         <v>1176</v>
       </c>
       <c r="B1178" s="2">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="C1178">
-        <v>3227.5</v>
+        <v>3222</v>
       </c>
       <c r="D1178">
-        <v>14525</v>
+        <v>14535</v>
       </c>
       <c r="E1178">
-        <v>1866</v>
+        <v>1880</v>
       </c>
       <c r="F1178">
-        <v>16895</v>
+        <v>16850</v>
       </c>
       <c r="G1178">
-        <v>4107</v>
+        <v>4070</v>
       </c>
       <c r="H1178">
-        <v>55300</v>
+        <v>55125</v>
       </c>
     </row>
     <row r="1179" spans="1:8">
@@ -31029,25 +31029,25 @@
         <v>1177</v>
       </c>
       <c r="B1179" s="2">
-        <v>46261</v>
+        <v>46266</v>
       </c>
       <c r="C1179">
-        <v>3212.5</v>
+        <v>3261</v>
       </c>
       <c r="D1179">
-        <v>14490</v>
+        <v>14395.5</v>
       </c>
       <c r="E1179">
-        <v>1872</v>
+        <v>1874</v>
       </c>
       <c r="F1179">
-        <v>16660</v>
+        <v>16350</v>
       </c>
       <c r="G1179">
-        <v>4107</v>
+        <v>4115</v>
       </c>
       <c r="H1179">
-        <v>54950</v>
+        <v>54725</v>
       </c>
     </row>
     <row r="1180" spans="1:8">
@@ -31055,25 +31055,25 @@
         <v>1178</v>
       </c>
       <c r="B1180" s="2">
-        <v>46262</v>
+        <v>46267</v>
       </c>
       <c r="C1180">
-        <v>3222</v>
+        <v>3255.5</v>
       </c>
       <c r="D1180">
-        <v>14535</v>
+        <v>14355</v>
       </c>
       <c r="E1180">
-        <v>1880</v>
+        <v>1873</v>
       </c>
       <c r="F1180">
-        <v>16850</v>
+        <v>16530</v>
       </c>
       <c r="G1180">
-        <v>4070</v>
+        <v>4000</v>
       </c>
       <c r="H1180">
-        <v>55125</v>
+        <v>53950</v>
       </c>
     </row>
     <row r="1181" spans="1:8">
@@ -31081,25 +31081,25 @@
         <v>1179</v>
       </c>
       <c r="B1181" s="2">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="C1181">
-        <v>3261</v>
+        <v>3303</v>
       </c>
       <c r="D1181">
-        <v>14395.5</v>
+        <v>14359</v>
       </c>
       <c r="E1181">
-        <v>1874</v>
+        <v>1870</v>
       </c>
       <c r="F1181">
-        <v>16350</v>
+        <v>16615</v>
       </c>
       <c r="G1181">
-        <v>4115</v>
+        <v>3995.5</v>
       </c>
       <c r="H1181">
-        <v>54725</v>
+        <v>54450</v>
       </c>
     </row>
     <row r="1182" spans="1:8">
@@ -31107,25 +31107,25 @@
         <v>1180</v>
       </c>
       <c r="B1182" s="2">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="C1182">
-        <v>3255.5</v>
+        <v>3292.5</v>
       </c>
       <c r="D1182">
-        <v>14355</v>
+        <v>14371</v>
       </c>
       <c r="E1182">
-        <v>1873</v>
+        <v>1871</v>
       </c>
       <c r="F1182">
-        <v>16530</v>
+        <v>16690</v>
       </c>
       <c r="G1182">
-        <v>4000</v>
+        <v>4087</v>
       </c>
       <c r="H1182">
-        <v>53950</v>
+        <v>54525</v>
       </c>
     </row>
     <row r="1183" spans="1:8">
@@ -31133,25 +31133,25 @@
         <v>1181</v>
       </c>
       <c r="B1183" s="2">
-        <v>46268</v>
+        <v>46272</v>
       </c>
       <c r="C1183">
-        <v>3303</v>
+        <v>3310</v>
       </c>
       <c r="D1183">
-        <v>14359</v>
+        <v>14540</v>
       </c>
       <c r="E1183">
-        <v>1870</v>
+        <v>1875</v>
       </c>
       <c r="F1183">
-        <v>16615</v>
+        <v>16600</v>
       </c>
       <c r="G1183">
-        <v>3995.5</v>
+        <v>4157</v>
       </c>
       <c r="H1183">
-        <v>54450</v>
+        <v>55100</v>
       </c>
     </row>
     <row r="1184" spans="1:8">
@@ -31159,25 +31159,25 @@
         <v>1182</v>
       </c>
       <c r="B1184" s="2">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="C1184">
-        <v>3292.5</v>
+        <v>3325</v>
       </c>
       <c r="D1184">
-        <v>14371</v>
+        <v>14737</v>
       </c>
       <c r="E1184">
-        <v>1871</v>
+        <v>1859</v>
       </c>
       <c r="F1184">
-        <v>16690</v>
+        <v>16675</v>
       </c>
       <c r="G1184">
-        <v>4087</v>
+        <v>4110</v>
       </c>
       <c r="H1184">
-        <v>54525</v>
+        <v>54900</v>
       </c>
     </row>
     <row r="1185" spans="1:8">
@@ -31185,25 +31185,25 @@
         <v>1183</v>
       </c>
       <c r="B1185" s="2">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="C1185">
-        <v>3310</v>
+        <v>3352</v>
       </c>
       <c r="D1185">
-        <v>14540</v>
+        <v>14672</v>
       </c>
       <c r="E1185">
-        <v>1875</v>
+        <v>1871</v>
       </c>
       <c r="F1185">
-        <v>16600</v>
+        <v>16675</v>
       </c>
       <c r="G1185">
-        <v>4157</v>
+        <v>4186</v>
       </c>
       <c r="H1185">
-        <v>55100</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="1186" spans="1:8">
@@ -31211,25 +31211,25 @@
         <v>1184</v>
       </c>
       <c r="B1186" s="2">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="C1186">
-        <v>3325</v>
+        <v>3343</v>
       </c>
       <c r="D1186">
-        <v>14737</v>
+        <v>14390</v>
       </c>
       <c r="E1186">
-        <v>1859</v>
+        <v>1870.5</v>
       </c>
       <c r="F1186">
-        <v>16675</v>
+        <v>16630</v>
       </c>
       <c r="G1186">
-        <v>4110</v>
+        <v>4105</v>
       </c>
       <c r="H1186">
-        <v>54900</v>
+        <v>54750</v>
       </c>
     </row>
     <row r="1187" spans="1:8">
@@ -31237,25 +31237,25 @@
         <v>1185</v>
       </c>
       <c r="B1187" s="2">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="C1187">
-        <v>3352</v>
+        <v>3274</v>
       </c>
       <c r="D1187">
-        <v>14672</v>
+        <v>14238.5</v>
       </c>
       <c r="E1187">
-        <v>1871</v>
+        <v>1854</v>
       </c>
       <c r="F1187">
-        <v>16675</v>
+        <v>16270</v>
       </c>
       <c r="G1187">
-        <v>4186</v>
+        <v>4015</v>
       </c>
       <c r="H1187">
-        <v>55000</v>
+        <v>53755</v>
       </c>
     </row>
     <row r="1188" spans="1:8">
@@ -31263,25 +31263,25 @@
         <v>1186</v>
       </c>
       <c r="B1188" s="2">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="C1188">
-        <v>3343</v>
+        <v>3311</v>
       </c>
       <c r="D1188">
-        <v>14390</v>
+        <v>14044</v>
       </c>
       <c r="E1188">
-        <v>1870.5</v>
+        <v>1834</v>
       </c>
       <c r="F1188">
-        <v>16630</v>
+        <v>16205</v>
       </c>
       <c r="G1188">
-        <v>4105</v>
+        <v>3951</v>
       </c>
       <c r="H1188">
-        <v>54750</v>
+        <v>52200</v>
       </c>
     </row>
     <row r="1189" spans="1:8">
@@ -31289,25 +31289,25 @@
         <v>1187</v>
       </c>
       <c r="B1189" s="2">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="C1189">
-        <v>3274</v>
+        <v>3260</v>
       </c>
       <c r="D1189">
-        <v>14238.5</v>
+        <v>14045</v>
       </c>
       <c r="E1189">
-        <v>1854</v>
+        <v>1829</v>
       </c>
       <c r="F1189">
-        <v>16270</v>
+        <v>16135</v>
       </c>
       <c r="G1189">
-        <v>4015</v>
+        <v>3922</v>
       </c>
       <c r="H1189">
-        <v>53755</v>
+        <v>51800</v>
       </c>
     </row>
     <row r="1190" spans="1:8">
@@ -31315,25 +31315,25 @@
         <v>1188</v>
       </c>
       <c r="B1190" s="2">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="C1190">
-        <v>3311</v>
+        <v>3310</v>
       </c>
       <c r="D1190">
-        <v>14044</v>
+        <v>14227</v>
       </c>
       <c r="E1190">
-        <v>1834</v>
+        <v>1848</v>
       </c>
       <c r="F1190">
-        <v>16205</v>
+        <v>16090</v>
       </c>
       <c r="G1190">
-        <v>3951</v>
+        <v>3937</v>
       </c>
       <c r="H1190">
-        <v>52200</v>
+        <v>52310</v>
       </c>
     </row>
     <row r="1191" spans="1:8">
@@ -31341,25 +31341,25 @@
         <v>1189</v>
       </c>
       <c r="B1191" s="2">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="C1191">
-        <v>3260</v>
+        <v>3303.5</v>
       </c>
       <c r="D1191">
-        <v>14045</v>
+        <v>14400.5</v>
       </c>
       <c r="E1191">
-        <v>1829</v>
+        <v>1862</v>
       </c>
       <c r="F1191">
-        <v>16135</v>
+        <v>16170</v>
       </c>
       <c r="G1191">
-        <v>3922</v>
+        <v>3941</v>
       </c>
       <c r="H1191">
-        <v>51800</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="1192" spans="1:8">
@@ -31367,25 +31367,25 @@
         <v>1190</v>
       </c>
       <c r="B1192" s="2">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="C1192">
-        <v>3310</v>
+        <v>3285</v>
       </c>
       <c r="D1192">
-        <v>14227</v>
+        <v>14529</v>
       </c>
       <c r="E1192">
-        <v>1848</v>
+        <v>1868</v>
       </c>
       <c r="F1192">
-        <v>16090</v>
+        <v>16055</v>
       </c>
       <c r="G1192">
-        <v>3937</v>
+        <v>4010</v>
       </c>
       <c r="H1192">
-        <v>52310</v>
+        <v>53600</v>
       </c>
     </row>
     <row r="1193" spans="1:8">
@@ -31393,25 +31393,25 @@
         <v>1191</v>
       </c>
       <c r="B1193" s="2">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="C1193">
-        <v>3303.5</v>
+        <v>3262.5</v>
       </c>
       <c r="D1193">
-        <v>14400.5</v>
+        <v>14788</v>
       </c>
       <c r="E1193">
-        <v>1862</v>
+        <v>1890</v>
       </c>
       <c r="F1193">
-        <v>16170</v>
+        <v>16125</v>
       </c>
       <c r="G1193">
-        <v>3941</v>
+        <v>4018</v>
       </c>
       <c r="H1193">
-        <v>53000</v>
+        <v>53785</v>
       </c>
     </row>
     <row r="1194" spans="1:8">
@@ -31419,25 +31419,25 @@
         <v>1192</v>
       </c>
       <c r="B1194" s="2">
-        <v>46283</v>
+        <v>46287</v>
       </c>
       <c r="C1194">
-        <v>3285</v>
+        <v>3242</v>
       </c>
       <c r="D1194">
-        <v>14529</v>
+        <v>14797</v>
       </c>
       <c r="E1194">
-        <v>1868</v>
+        <v>1909</v>
       </c>
       <c r="F1194">
-        <v>16055</v>
+        <v>16410</v>
       </c>
       <c r="G1194">
-        <v>4010</v>
+        <v>4006</v>
       </c>
       <c r="H1194">
-        <v>53600</v>
+        <v>53745</v>
       </c>
     </row>
     <row r="1195" spans="1:8">
@@ -31445,25 +31445,25 @@
         <v>1193</v>
       </c>
       <c r="B1195" s="2">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="C1195">
-        <v>3262.5</v>
+        <v>3240</v>
       </c>
       <c r="D1195">
-        <v>14788</v>
+        <v>14735</v>
       </c>
       <c r="E1195">
-        <v>1890</v>
+        <v>1885.5</v>
       </c>
       <c r="F1195">
-        <v>16125</v>
+        <v>16430</v>
       </c>
       <c r="G1195">
-        <v>4018</v>
+        <v>3949</v>
       </c>
       <c r="H1195">
-        <v>53785</v>
+        <v>54050</v>
       </c>
     </row>
     <row r="1196" spans="1:8">
@@ -31471,25 +31471,25 @@
         <v>1194</v>
       </c>
       <c r="B1196" s="2">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="C1196">
-        <v>3242</v>
+        <v>3228</v>
       </c>
       <c r="D1196">
-        <v>14797</v>
+        <v>14765</v>
       </c>
       <c r="E1196">
-        <v>1909</v>
+        <v>1900</v>
       </c>
       <c r="F1196">
-        <v>16410</v>
+        <v>16320</v>
       </c>
       <c r="G1196">
-        <v>4006</v>
+        <v>3981</v>
       </c>
       <c r="H1196">
-        <v>53745</v>
+        <v>53875</v>
       </c>
     </row>
     <row r="1197" spans="1:8">
@@ -31497,25 +31497,25 @@
         <v>1195</v>
       </c>
       <c r="B1197" s="2">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="C1197">
-        <v>3240</v>
+        <v>3254</v>
       </c>
       <c r="D1197">
-        <v>14735</v>
+        <v>14740</v>
       </c>
       <c r="E1197">
-        <v>1885.5</v>
+        <v>1902.5</v>
       </c>
       <c r="F1197">
-        <v>16430</v>
+        <v>16050</v>
       </c>
       <c r="G1197">
-        <v>3949</v>
+        <v>4060</v>
       </c>
       <c r="H1197">
-        <v>54050</v>
+        <v>54025</v>
       </c>
     </row>
     <row r="1198" spans="1:8">
@@ -31523,25 +31523,25 @@
         <v>1196</v>
       </c>
       <c r="B1198" s="2">
-        <v>46289</v>
+        <v>46293</v>
       </c>
       <c r="C1198">
-        <v>3228</v>
+        <v>3248.5</v>
       </c>
       <c r="D1198">
-        <v>14765</v>
+        <v>14544.5</v>
       </c>
       <c r="E1198">
-        <v>1900</v>
+        <v>1886</v>
       </c>
       <c r="F1198">
-        <v>16320</v>
+        <v>16050</v>
       </c>
       <c r="G1198">
-        <v>3981</v>
+        <v>3957</v>
       </c>
       <c r="H1198">
-        <v>53875</v>
+        <v>53750</v>
       </c>
     </row>
     <row r="1199" spans="1:8">
@@ -31549,25 +31549,25 @@
         <v>1197</v>
       </c>
       <c r="B1199" s="2">
-        <v>46290</v>
+        <v>46294</v>
       </c>
       <c r="C1199">
-        <v>3254</v>
+        <v>3225.5</v>
       </c>
       <c r="D1199">
-        <v>14740</v>
+        <v>14474.5</v>
       </c>
       <c r="E1199">
-        <v>1902.5</v>
+        <v>1876</v>
       </c>
       <c r="F1199">
-        <v>16050</v>
+        <v>15860</v>
       </c>
       <c r="G1199">
-        <v>4060</v>
+        <v>3977</v>
       </c>
       <c r="H1199">
-        <v>54025</v>
+        <v>53950</v>
       </c>
     </row>
     <row r="1200" spans="1:8">
@@ -31575,76 +31575,24 @@
         <v>1198</v>
       </c>
       <c r="B1200" s="2">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="C1200">
-        <v>3248.5</v>
+        <v>3204</v>
       </c>
       <c r="D1200">
-        <v>14544.5</v>
+        <v>14487</v>
       </c>
       <c r="E1200">
-        <v>1886</v>
+        <v>1856</v>
       </c>
       <c r="F1200">
-        <v>16050</v>
+        <v>15860</v>
       </c>
       <c r="G1200">
-        <v>3957</v>
+        <v>3954</v>
       </c>
       <c r="H1200">
-        <v>53750</v>
-      </c>
-    </row>
-    <row r="1201" spans="1:8">
-      <c r="A1201" s="1">
-        <v>1199</v>
-      </c>
-      <c r="B1201" s="2">
-        <v>46294</v>
-      </c>
-      <c r="C1201">
-        <v>3225.5</v>
-      </c>
-      <c r="D1201">
-        <v>14474.5</v>
-      </c>
-      <c r="E1201">
-        <v>1876</v>
-      </c>
-      <c r="F1201">
-        <v>15860</v>
-      </c>
-      <c r="G1201">
-        <v>3977</v>
-      </c>
-      <c r="H1201">
-        <v>53950</v>
-      </c>
-    </row>
-    <row r="1202" spans="1:8">
-      <c r="A1202" s="1">
-        <v>1200</v>
-      </c>
-      <c r="B1202" s="2">
-        <v>46295</v>
-      </c>
-      <c r="C1202">
-        <v>3204</v>
-      </c>
-      <c r="D1202">
-        <v>14487</v>
-      </c>
-      <c r="E1202">
-        <v>1856</v>
-      </c>
-      <c r="F1202">
-        <v>15860</v>
-      </c>
-      <c r="G1202">
-        <v>3954</v>
-      </c>
-      <c r="H1202">
         <v>54075</v>
       </c>
     </row>

--- a/LME/parser/westmetall/data/LME_westmetall_db.xlsx
+++ b/LME/parser/westmetall/data/LME_westmetall_db.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1200"/>
+  <dimension ref="A1:H1201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -31596,6 +31596,32 @@
         <v>54075</v>
       </c>
     </row>
+    <row r="1201" spans="1:8">
+      <c r="A1201" s="1">
+        <v>1199</v>
+      </c>
+      <c r="B1201" s="2">
+        <v>46296</v>
+      </c>
+      <c r="C1201">
+        <v>3120</v>
+      </c>
+      <c r="D1201">
+        <v>14335</v>
+      </c>
+      <c r="E1201">
+        <v>1837</v>
+      </c>
+      <c r="F1201">
+        <v>15570</v>
+      </c>
+      <c r="G1201">
+        <v>3834</v>
+      </c>
+      <c r="H1201">
+        <v>54400</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/westmetall/data/LME_westmetall_db.xlsx
+++ b/LME/parser/westmetall/data/LME_westmetall_db.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1201"/>
+  <dimension ref="A1:H1202"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -31622,6 +31622,32 @@
         <v>54400</v>
       </c>
     </row>
+    <row r="1202" spans="1:8">
+      <c r="A1202" s="1">
+        <v>1200</v>
+      </c>
+      <c r="B1202" s="2">
+        <v>46297</v>
+      </c>
+      <c r="C1202">
+        <v>3109.5</v>
+      </c>
+      <c r="D1202">
+        <v>14355</v>
+      </c>
+      <c r="E1202">
+        <v>1827</v>
+      </c>
+      <c r="F1202">
+        <v>15435</v>
+      </c>
+      <c r="G1202">
+        <v>3798</v>
+      </c>
+      <c r="H1202">
+        <v>54355</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/westmetall/data/LME_westmetall_db.xlsx
+++ b/LME/parser/westmetall/data/LME_westmetall_db.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1202"/>
+  <dimension ref="A1:H1203"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -31648,6 +31648,32 @@
         <v>54355</v>
       </c>
     </row>
+    <row r="1203" spans="1:8">
+      <c r="A1203" s="1">
+        <v>1201</v>
+      </c>
+      <c r="B1203" s="2">
+        <v>46300</v>
+      </c>
+      <c r="C1203">
+        <v>3107</v>
+      </c>
+      <c r="D1203">
+        <v>14430</v>
+      </c>
+      <c r="E1203">
+        <v>1829.5</v>
+      </c>
+      <c r="F1203">
+        <v>15470</v>
+      </c>
+      <c r="G1203">
+        <v>3774</v>
+      </c>
+      <c r="H1203">
+        <v>54250</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/westmetall/data/LME_westmetall_db.xlsx
+++ b/LME/parser/westmetall/data/LME_westmetall_db.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1203"/>
+  <dimension ref="A1:H1204"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -31674,6 +31674,32 @@
         <v>54250</v>
       </c>
     </row>
+    <row r="1204" spans="1:8">
+      <c r="A1204" s="1">
+        <v>1202</v>
+      </c>
+      <c r="B1204" s="2">
+        <v>46301</v>
+      </c>
+      <c r="C1204">
+        <v>3134.5</v>
+      </c>
+      <c r="D1204">
+        <v>14505</v>
+      </c>
+      <c r="E1204">
+        <v>1837.5</v>
+      </c>
+      <c r="F1204">
+        <v>15530</v>
+      </c>
+      <c r="G1204">
+        <v>3803</v>
+      </c>
+      <c r="H1204">
+        <v>54275</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/westmetall/data/LME_westmetall_db.xlsx
+++ b/LME/parser/westmetall/data/LME_westmetall_db.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1204"/>
+  <dimension ref="A1:H1205"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -31700,6 +31700,32 @@
         <v>54275</v>
       </c>
     </row>
+    <row r="1205" spans="1:8">
+      <c r="A1205" s="1">
+        <v>1203</v>
+      </c>
+      <c r="B1205" s="2">
+        <v>46302</v>
+      </c>
+      <c r="C1205">
+        <v>3102.5</v>
+      </c>
+      <c r="D1205">
+        <v>14510</v>
+      </c>
+      <c r="E1205">
+        <v>1844.5</v>
+      </c>
+      <c r="F1205">
+        <v>15645</v>
+      </c>
+      <c r="G1205">
+        <v>3799</v>
+      </c>
+      <c r="H1205">
+        <v>54000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/westmetall/data/LME_westmetall_db.xlsx
+++ b/LME/parser/westmetall/data/LME_westmetall_db.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1205"/>
+  <dimension ref="A1:H1206"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -31726,6 +31726,32 @@
         <v>54000</v>
       </c>
     </row>
+    <row r="1206" spans="1:8">
+      <c r="A1206" s="1">
+        <v>1204</v>
+      </c>
+      <c r="B1206" s="2">
+        <v>46303</v>
+      </c>
+      <c r="C1206">
+        <v>3060.5</v>
+      </c>
+      <c r="D1206">
+        <v>14526</v>
+      </c>
+      <c r="E1206">
+        <v>1833</v>
+      </c>
+      <c r="F1206">
+        <v>15415</v>
+      </c>
+      <c r="G1206">
+        <v>3781</v>
+      </c>
+      <c r="H1206">
+        <v>53050</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/westmetall/data/LME_westmetall_db.xlsx
+++ b/LME/parser/westmetall/data/LME_westmetall_db.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1206"/>
+  <dimension ref="A1:H1207"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -31752,6 +31752,32 @@
         <v>53050</v>
       </c>
     </row>
+    <row r="1207" spans="1:8">
+      <c r="A1207" s="1">
+        <v>1205</v>
+      </c>
+      <c r="B1207" s="2">
+        <v>46304</v>
+      </c>
+      <c r="C1207">
+        <v>3055.5</v>
+      </c>
+      <c r="D1207">
+        <v>14689</v>
+      </c>
+      <c r="E1207">
+        <v>1847</v>
+      </c>
+      <c r="F1207">
+        <v>15545</v>
+      </c>
+      <c r="G1207">
+        <v>3840</v>
+      </c>
+      <c r="H1207">
+        <v>52900</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/westmetall/data/LME_westmetall_db.xlsx
+++ b/LME/parser/westmetall/data/LME_westmetall_db.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1207"/>
+  <dimension ref="A1:H1208"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -31778,6 +31778,32 @@
         <v>52900</v>
       </c>
     </row>
+    <row r="1208" spans="1:8">
+      <c r="A1208" s="1">
+        <v>1206</v>
+      </c>
+      <c r="B1208" s="2">
+        <v>46307</v>
+      </c>
+      <c r="C1208">
+        <v>3055</v>
+      </c>
+      <c r="D1208">
+        <v>14822</v>
+      </c>
+      <c r="E1208">
+        <v>1842</v>
+      </c>
+      <c r="F1208">
+        <v>15515</v>
+      </c>
+      <c r="G1208">
+        <v>3811</v>
+      </c>
+      <c r="H1208">
+        <v>53500</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/westmetall/data/LME_westmetall_db.xlsx
+++ b/LME/parser/westmetall/data/LME_westmetall_db.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1208"/>
+  <dimension ref="A1:H1209"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -31804,6 +31804,32 @@
         <v>53500</v>
       </c>
     </row>
+    <row r="1209" spans="1:8">
+      <c r="A1209" s="1">
+        <v>1207</v>
+      </c>
+      <c r="B1209" s="2">
+        <v>46308</v>
+      </c>
+      <c r="C1209">
+        <v>3036</v>
+      </c>
+      <c r="D1209">
+        <v>14741</v>
+      </c>
+      <c r="E1209">
+        <v>1860</v>
+      </c>
+      <c r="F1209">
+        <v>15445</v>
+      </c>
+      <c r="G1209">
+        <v>3821</v>
+      </c>
+      <c r="H1209">
+        <v>53000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/westmetall/data/LME_westmetall_db.xlsx
+++ b/LME/parser/westmetall/data/LME_westmetall_db.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1209"/>
+  <dimension ref="A1:H1210"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -31830,6 +31830,32 @@
         <v>53000</v>
       </c>
     </row>
+    <row r="1210" spans="1:8">
+      <c r="A1210" s="1">
+        <v>1208</v>
+      </c>
+      <c r="B1210" s="2">
+        <v>46309</v>
+      </c>
+      <c r="C1210">
+        <v>3010</v>
+      </c>
+      <c r="D1210">
+        <v>14751</v>
+      </c>
+      <c r="E1210">
+        <v>1866</v>
+      </c>
+      <c r="F1210">
+        <v>15475</v>
+      </c>
+      <c r="G1210">
+        <v>3803</v>
+      </c>
+      <c r="H1210">
+        <v>51100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/westmetall/data/LME_westmetall_db.xlsx
+++ b/LME/parser/westmetall/data/LME_westmetall_db.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1210"/>
+  <dimension ref="A1:H1211"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -31856,6 +31856,32 @@
         <v>51100</v>
       </c>
     </row>
+    <row r="1211" spans="1:8">
+      <c r="A1211" s="1">
+        <v>1209</v>
+      </c>
+      <c r="B1211" s="2">
+        <v>46310</v>
+      </c>
+      <c r="C1211">
+        <v>2999</v>
+      </c>
+      <c r="D1211">
+        <v>14539</v>
+      </c>
+      <c r="E1211">
+        <v>1853</v>
+      </c>
+      <c r="F1211">
+        <v>14885</v>
+      </c>
+      <c r="G1211">
+        <v>3724</v>
+      </c>
+      <c r="H1211">
+        <v>50100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/westmetall/data/LME_westmetall_db.xlsx
+++ b/LME/parser/westmetall/data/LME_westmetall_db.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1211"/>
+  <dimension ref="A1:H1212"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -31882,6 +31882,32 @@
         <v>50100</v>
       </c>
     </row>
+    <row r="1212" spans="1:8">
+      <c r="A1212" s="1">
+        <v>1210</v>
+      </c>
+      <c r="B1212" s="2">
+        <v>46311</v>
+      </c>
+      <c r="C1212">
+        <v>3014</v>
+      </c>
+      <c r="D1212">
+        <v>14595</v>
+      </c>
+      <c r="E1212">
+        <v>1854</v>
+      </c>
+      <c r="F1212">
+        <v>15170</v>
+      </c>
+      <c r="G1212">
+        <v>3739</v>
+      </c>
+      <c r="H1212">
+        <v>50700</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/westmetall/data/LME_westmetall_db.xlsx
+++ b/LME/parser/westmetall/data/LME_westmetall_db.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1212"/>
+  <dimension ref="A1:H1213"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -31908,6 +31908,32 @@
         <v>50700</v>
       </c>
     </row>
+    <row r="1213" spans="1:8">
+      <c r="A1213" s="1">
+        <v>1211</v>
+      </c>
+      <c r="B1213" s="2">
+        <v>46314</v>
+      </c>
+      <c r="C1213">
+        <v>3019</v>
+      </c>
+      <c r="D1213">
+        <v>14496</v>
+      </c>
+      <c r="E1213">
+        <v>1856</v>
+      </c>
+      <c r="F1213">
+        <v>15275</v>
+      </c>
+      <c r="G1213">
+        <v>3776</v>
+      </c>
+      <c r="H1213">
+        <v>51045</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/westmetall/data/LME_westmetall_db.xlsx
+++ b/LME/parser/westmetall/data/LME_westmetall_db.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1213"/>
+  <dimension ref="A1:H1214"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -31934,6 +31934,32 @@
         <v>51045</v>
       </c>
     </row>
+    <row r="1214" spans="1:8">
+      <c r="A1214" s="1">
+        <v>1212</v>
+      </c>
+      <c r="B1214" s="2">
+        <v>46315</v>
+      </c>
+      <c r="C1214">
+        <v>3003.5</v>
+      </c>
+      <c r="D1214">
+        <v>14540</v>
+      </c>
+      <c r="E1214">
+        <v>1851</v>
+      </c>
+      <c r="F1214">
+        <v>15350</v>
+      </c>
+      <c r="G1214">
+        <v>3736</v>
+      </c>
+      <c r="H1214">
+        <v>51200</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/westmetall/data/LME_westmetall_db.xlsx
+++ b/LME/parser/westmetall/data/LME_westmetall_db.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1214"/>
+  <dimension ref="A1:H1215"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -31960,6 +31960,32 @@
         <v>51200</v>
       </c>
     </row>
+    <row r="1215" spans="1:8">
+      <c r="A1215" s="1">
+        <v>1213</v>
+      </c>
+      <c r="B1215" s="2">
+        <v>46316</v>
+      </c>
+      <c r="C1215">
+        <v>3031</v>
+      </c>
+      <c r="D1215">
+        <v>14441</v>
+      </c>
+      <c r="E1215">
+        <v>1880</v>
+      </c>
+      <c r="F1215">
+        <v>15830</v>
+      </c>
+      <c r="G1215">
+        <v>3771</v>
+      </c>
+      <c r="H1215">
+        <v>51550</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/westmetall/data/LME_westmetall_db.xlsx
+++ b/LME/parser/westmetall/data/LME_westmetall_db.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1215"/>
+  <dimension ref="A1:H1216"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -31986,6 +31986,32 @@
         <v>51550</v>
       </c>
     </row>
+    <row r="1216" spans="1:8">
+      <c r="A1216" s="1">
+        <v>1214</v>
+      </c>
+      <c r="B1216" s="2">
+        <v>46317</v>
+      </c>
+      <c r="C1216">
+        <v>3033</v>
+      </c>
+      <c r="D1216">
+        <v>14215</v>
+      </c>
+      <c r="E1216">
+        <v>1872</v>
+      </c>
+      <c r="F1216">
+        <v>15935</v>
+      </c>
+      <c r="G1216">
+        <v>3727</v>
+      </c>
+      <c r="H1216">
+        <v>50150</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/westmetall/data/LME_westmetall_db.xlsx
+++ b/LME/parser/westmetall/data/LME_westmetall_db.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1216"/>
+  <dimension ref="A1:H1217"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -32012,6 +32012,32 @@
         <v>50150</v>
       </c>
     </row>
+    <row r="1217" spans="1:8">
+      <c r="A1217" s="1">
+        <v>1215</v>
+      </c>
+      <c r="B1217" s="2">
+        <v>46318</v>
+      </c>
+      <c r="C1217">
+        <v>3043</v>
+      </c>
+      <c r="D1217">
+        <v>14415</v>
+      </c>
+      <c r="E1217">
+        <v>1886</v>
+      </c>
+      <c r="F1217">
+        <v>15695</v>
+      </c>
+      <c r="G1217">
+        <v>3790</v>
+      </c>
+      <c r="H1217">
+        <v>50855</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/westmetall/data/LME_westmetall_db.xlsx
+++ b/LME/parser/westmetall/data/LME_westmetall_db.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1217"/>
+  <dimension ref="A1:H1218"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -32038,6 +32038,32 @@
         <v>50855</v>
       </c>
     </row>
+    <row r="1218" spans="1:8">
+      <c r="A1218" s="1">
+        <v>1216</v>
+      </c>
+      <c r="B1218" s="2">
+        <v>46321</v>
+      </c>
+      <c r="C1218">
+        <v>3047.5</v>
+      </c>
+      <c r="D1218">
+        <v>14500</v>
+      </c>
+      <c r="E1218">
+        <v>1900</v>
+      </c>
+      <c r="F1218">
+        <v>15535</v>
+      </c>
+      <c r="G1218">
+        <v>3900</v>
+      </c>
+      <c r="H1218">
+        <v>50925</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/westmetall/data/LME_westmetall_db.xlsx
+++ b/LME/parser/westmetall/data/LME_westmetall_db.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1218"/>
+  <dimension ref="A1:H1219"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -32064,6 +32064,32 @@
         <v>50925</v>
       </c>
     </row>
+    <row r="1219" spans="1:8">
+      <c r="A1219" s="1">
+        <v>1217</v>
+      </c>
+      <c r="B1219" s="2">
+        <v>46322</v>
+      </c>
+      <c r="C1219">
+        <v>3078</v>
+      </c>
+      <c r="D1219">
+        <v>14625</v>
+      </c>
+      <c r="E1219">
+        <v>1900</v>
+      </c>
+      <c r="F1219">
+        <v>15440</v>
+      </c>
+      <c r="G1219">
+        <v>3927</v>
+      </c>
+      <c r="H1219">
+        <v>51300</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/westmetall/data/LME_westmetall_db.xlsx
+++ b/LME/parser/westmetall/data/LME_westmetall_db.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1219"/>
+  <dimension ref="A1:H1220"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -32090,6 +32090,32 @@
         <v>51300</v>
       </c>
     </row>
+    <row r="1220" spans="1:8">
+      <c r="A1220" s="1">
+        <v>1218</v>
+      </c>
+      <c r="B1220" s="2">
+        <v>46323</v>
+      </c>
+      <c r="C1220">
+        <v>3101</v>
+      </c>
+      <c r="D1220">
+        <v>14675.5</v>
+      </c>
+      <c r="E1220">
+        <v>1910</v>
+      </c>
+      <c r="F1220">
+        <v>15580</v>
+      </c>
+      <c r="G1220">
+        <v>3960</v>
+      </c>
+      <c r="H1220">
+        <v>51700</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/westmetall/data/LME_westmetall_db.xlsx
+++ b/LME/parser/westmetall/data/LME_westmetall_db.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1220"/>
+  <dimension ref="A1:H1221"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -32116,6 +32116,32 @@
         <v>51700</v>
       </c>
     </row>
+    <row r="1221" spans="1:8">
+      <c r="A1221" s="1">
+        <v>1219</v>
+      </c>
+      <c r="B1221" s="2">
+        <v>46324</v>
+      </c>
+      <c r="C1221">
+        <v>3071</v>
+      </c>
+      <c r="D1221">
+        <v>14560</v>
+      </c>
+      <c r="E1221">
+        <v>1878</v>
+      </c>
+      <c r="F1221">
+        <v>15360</v>
+      </c>
+      <c r="G1221">
+        <v>3980</v>
+      </c>
+      <c r="H1221">
+        <v>50400</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser/westmetall/data/LME_westmetall_db.xlsx
+++ b/LME/parser/westmetall/data/LME_westmetall_db.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1221"/>
+  <dimension ref="A1:H1222"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -32142,6 +32142,32 @@
         <v>50400</v>
       </c>
     </row>
+    <row r="1222" spans="1:8">
+      <c r="A1222" s="1">
+        <v>1220</v>
+      </c>
+      <c r="B1222" s="2">
+        <v>46325</v>
+      </c>
+      <c r="C1222">
+        <v>3114</v>
+      </c>
+      <c r="D1222">
+        <v>14449</v>
+      </c>
+      <c r="E1222">
+        <v>1890</v>
+      </c>
+      <c r="F1222">
+        <v>15240</v>
+      </c>
+      <c r="G1222">
+        <v>3955.5</v>
+      </c>
+      <c r="H1222">
+        <v>48795</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
